--- a/docs/case_files/CASE_IDOL.xlsx
+++ b/docs/case_files/CASE_IDOL.xlsx
@@ -3455,6 +3455,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="29">
       <c r="A3" s="55" t="inlineStr">
         <is>
@@ -3480,7 +3481,7 @@
     <row r="4" ht="15" customHeight="1" s="29">
       <c r="A4" s="33" t="inlineStr">
         <is>
-          <t>~07-27→08-01</t>
+          <t>31/07→02/08</t>
         </is>
       </c>
       <c r="B4" s="33" t="inlineStr">
@@ -3495,7 +3496,7 @@
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>PENDING-VERIFY: txhash + ngay chinh xac + dich 58bro + label-check</t>
+          <t>PENDING-VERIFY: txhash + ngay chinh xac tu Nansen. Doc: rut TRONG markup (gia len 0.016→0.024 01-02/08) — hai khuon canh tranh: (1) that float leg-2 (ESPORTS-10% pattern) vs (2) chot chien loi pham on-chain. E1 han cap -&gt; P3: can operator feed dia chi + txhash de phan loai.</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3518,7 @@
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>PENDING-VERIFY: txhash + ma tran BTW-vs-IDOL (B5 chu ky MARKUP da xac nhan?)</t>
+          <t>[HA CAP] &lt;2% supply — khong dang ke tren on-chain thesis. Giu dong lam vet. PENDING-VERIFY: txhash + phan loai BTW-vs-IDOL (Gate wallet 0x0d0707 co phai cung operator BTW khong?)</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="28" min="1" max="1"/>
@@ -3570,6 +3571,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="29">
       <c r="A3" s="55" t="inlineStr">
         <is>
@@ -3598,32 +3600,112 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="33" t="n"/>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="34" t="n"/>
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Redeposit bat ky vi nao trong cum 13</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Bat ky vi trong cum 13 ~273M gui lai len san (BscScan detect)</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>DONG AN XA TUC THOI — tiet lo y dinh muon ban; khong gia han wait</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>CHUA BAT — watcher 0-credit pending B5</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="33" t="n"/>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="34" t="n"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>gLSR flush &lt;=1.1 + funding tai ghin &gt;=3d</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>glsr &lt;= 1.1 lien tuc &gt;=3 nen VA f_avg &lt;= 5e-5 &gt;=3 nen</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Ho so re-staging leg-2 song — theo doi luc luong crowd short nap nhien lieu</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>THEO DOI — 02/08 glsr=1.1436 (can them 03/08 de confirm trend)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="34" t="n"/>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>pos_r floor hau-sap</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>pos_r &gt;= 1.6 tai OI floor = con ghe (dinh luat #9); ga &lt; 1.3 = ghe rong</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>Con ghe -&gt; re-staging kha thi; Ghe rong -&gt; dong an/tra gia gap</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>THEO DOI — 02/08 pos_r=1.731 (&gt; 1.6, con ghe); OI=10.48M; cho 03/08</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="34" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Suppressor bat ky (L-27 §5)</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>dist_wall &lt; L-27_thresh HOAC neg_div ben &gt;= 3d HOAC post_climax flag</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>STAND_ASIDE — khong vao/them bat ke phe nao</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>CHO SO — cols 23/24 chua co gia tri (formula chua tinh)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3772,7 +3854,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>PENDING — fn=1 chua co du lieu sach 28-31/07; can serie sach sau ignition</t>
+          <t>Sau markup 01/08 (+50% 1 nen), f_avg 02/08 = 5e-5 (san/pinned). Trong nghia: MM chu dong de gim funding ve san sau markup — crowd khong chase (khong co premium demand); CONSISTENT EVAA khuon (re-staging, khong phai climax). Taker 01/08 = 51.5% (&lt;55%) = bid-walk, khong drive up funding. VAN TAY: pin-post-markup + taker&lt;55% = BIDWALK-A fingerprint.</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3866,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>PENDING — 3 van tay cho chot (bid-walk? bait-probe? staging-that?)</t>
+          <t>01/08: vol_q=175.67M (~10x nen binh quan 28-31/07 ~17M), taker=51.5% (duoi 55% suot ca cu markup) — bid-walk ro rang. OI: 27/07 6.60M → 28/07 10.71M (+62%) → 01/08 9.84M → 02/08 10.48M. pos_r: leo 2.059→2.558 truoc ignition, sap 2.524→1.731 sau markup. Timing: top longs loaded 28-31/07 (pre-ignition), exit 02/08 khi crowd gap vao (OI tang nhung pos_r sap). KHUON NGHI VAN: BIDWALK-A (bid limit trong khi taker bearish/neutral).</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3878,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>PENDING — 07-23 vol spike 167M (8x nen) nghi bait-probe; can vol_persistence T+1 xac nhan</t>
+          <t>23/07 vol spike (167M, 8x nen) - bait-probe NGHI VAN (can taker 23/07). 28/07 OI +62% nhung taker=0.480 (bear) = MM mua limit trong khi retail sell. 01/08 markup: taker 51.5% — crowd KHONG phat hien hoac khong dan vao, MM lam gia don gian. 31/07→02/08 rut on-chain 273M TRONG markup = phuc tap: hoac thang float (giam supply san), hoac chot loi on-chain. gLSR: 1.369→1.038 (28/07, crowd giam short) → leo 1.558 (31/07) → sap 1.144 (02/08, crowd tiep tuc unwind).</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3914,7 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>PENDING — ma tran BTW-vs-IDOL (Gate wallet 0x0d0707 co lien he BTW khong?)</t>
+          <t>PENDING — ma tran BTW-vs-IDOL: Gate wallet 0x0d0707 co lien he BTW khong? E2 ha cap (&lt;2% supply) nhung van giu vet de check cross-campaign. Can: operator feed txhash va label cho 0x0d0707.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3926,7 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>PENDING — theo doi sau khi infra_gate label-check xong</t>
+          <t>MM_ID: unknown-IDOL (nghi BIDWALK-A khuon). Du kien 3 van tay can xac nhan: (1) BIDWALK-A: markup taker&lt;55% DONE (01/08 = 51.5%); (2) Bait-probe: vol spike 23/07, PENDING taker; (3) On-chain staging: 7 vi x20M Sent=0 — DONE (giong BANK). Neu bait-probe confirm: so sanh voi AKE/BANK MM_BOOK. Verdict MM_ID: TAM THOI BIDWALK-A, cho them du lieu.</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_IDOL.xlsx
+++ b/docs/case_files/CASE_IDOL.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CASE" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +15,7 @@
     <sheet name="UNLOCK" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -31,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -41,49 +40,29 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
@@ -91,7 +70,6 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -177,192 +155,66 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="56">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -421,6 +273,14 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FF404040"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -500,41 +360,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -542,12 +402,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -576,7 +436,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -597,7 +457,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -648,7 +508,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -666,3382 +526,3869 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="26" customWidth="1" style="28" min="1" max="1"/>
-    <col width="100" customWidth="1" style="28" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CASE FILE — IDOL</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="29">
-      <c r="A2" s="28" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>oi_vs_med14 Excel != dinh nghia fire — window ending khac signals.py (signals.py dung window ket thuc ngay-truoc-check; DAILY dung window khac, chi nhin nhanh)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Nguon: case_tracker v1.1 · verdict chi operator ghi · so kem nguon · PENDING khong doan</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29"/>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="32" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bsc_contract_address</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x3b4de3c7855c03bb9f50ea252cd2c9fa1125ab07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>OPEN — WATCH-nong</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="32" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Loai</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>pump-setup vong 2 (sau ARMED#1 cu)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="32" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ngay phat hien</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>27-28/07: 2 vi consolidate 17M -&gt; 0x34828d + 3 vi rut ~$26M khoi Gate/48h</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="A8" s="32" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>chua xac dinh (ung vien 07-27/28 neu stealth giu) · px 28/07 ~0.00139</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="A9" s="32" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>action_class</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>WATCH — CHUA tai-ARM (thieu manh cau truc); KHONG duoi gia +40% (bai TUT/BULLA)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="A10" s="32" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Vi the</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Tom tat input</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>Gate probe: V thang 7 ~$15.6M &lt; $26M -&gt; KHONG THE gom tren Gate, inventory co san · book $2.5k/$1.2k = bai do · 0 cum BotAccum · nen 28/07: stealth_grind ban (margin mong), gLSR 1.71-&gt;1.30 wash-by-rally, pos hoi 1.595, div bung ~1.6 (avg3 1.34 chua dat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Gate probe: V thang 7 ~$15.6M &lt; $26M -&gt; KHONG THE gom tren Gate, inventory co san · book $2.5k/$1.2k = bai do · 0 cum BotAccum · nen 28/07: stealth_grind ban (margin mong), gLSR 1.71-&gt;1.30 wash-by-rally, pos hoi 1.595, div bung ~1.6 (avg3 1.34 chua dat) | [Z4-rev 03/08] W6 GOM-qua-Alpha = PLAUSIBLE (giả thuyết dẫn đầu). Z7: IDOL no_spot Binance, no Binance Alpha listing — nhưng Binance có thể là broker/custodian BSC. VWAP DEX proxy $0.018912 (Z6, 50/50). CG 03/08: PSv3-BSC $5.98M, Gate $1.12M, LBank $1.24M/24h. PENDING Z1: txhash 13 ví đích → confirm cơ chế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Verdict (operator)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>campaign nhieu kha nang tai khoi dong; 1 tell + accelerant, thieu 2 manh cau truc -&gt; chua ARMED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Dieu gi chung minh SAI</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>redeposit tu bat ky vi nao cum 6 · gia &lt;0.00072 · gLSR quay len &gt;1.5 kem gia dung</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="39.75" customHeight="1" s="29"/>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+    <row r="14" ht="39.75" customHeight="1"/>
+    <row r="15" ht="22.8" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">O vang = operator dien/quyet · Header nau vang (sheet DAILY) = cot manual · Dong to cam (DAILY) = data_bad=1, so mang sai so · Cot cong thuc (ret_1d, div, slope, oi_vs_med14, alpha) tu tinh khi may append dong moi — copy cong thuc dong tren xuong. </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AO32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10" customWidth="1" style="28" min="1" max="1"/>
-    <col width="11" customWidth="1" style="28" min="2" max="2"/>
-    <col width="8" customWidth="1" style="28" min="3" max="3"/>
-    <col width="13" customWidth="1" style="28" min="4" max="4"/>
-    <col width="9" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="8"/>
-    <col width="5" customWidth="1" style="28" min="9" max="9"/>
-    <col width="12" customWidth="1" style="28" min="10" max="10"/>
-    <col width="7" customWidth="1" style="28" min="11" max="11"/>
-    <col width="13" customWidth="1" style="28" min="12" max="12"/>
-    <col width="9" customWidth="1" style="28" min="13" max="17"/>
-    <col width="8" customWidth="1" style="28" min="18" max="19"/>
-    <col width="9" customWidth="1" style="28" min="20" max="20"/>
-    <col width="8" customWidth="1" style="28" min="21" max="22"/>
-    <col width="22" customWidth="1" style="28" min="23" max="23"/>
-    <col width="16" customWidth="1" style="28" min="24" max="24"/>
-    <col width="8" customWidth="1" style="28" min="25" max="25"/>
-    <col width="7" customWidth="1" style="28" min="26" max="26"/>
-    <col width="9" customWidth="1" style="28" min="27" max="27"/>
-    <col width="12" customWidth="1" style="28" min="28" max="28"/>
-    <col width="9" customWidth="1" style="28" min="29" max="29"/>
-    <col width="11" customWidth="1" style="28" min="30" max="35"/>
-    <col width="9" customWidth="1" style="28" min="36" max="36"/>
-    <col width="14" customWidth="1" style="28" min="37" max="37"/>
-    <col width="18" customWidth="1" style="28" min="38" max="38"/>
-    <col width="9" customWidth="1" style="28" min="39" max="39"/>
-    <col width="30" customWidth="1" style="28" min="40" max="40"/>
-    <col width="22" customWidth="1" style="28" min="41" max="41"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="12" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="11" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="3.44140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="9.44140625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="12" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="8.5546875" bestFit="1" customWidth="1" min="15" max="16"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="12" bestFit="1" customWidth="1" min="18" max="19"/>
+    <col width="12.21875" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="12" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="12.88671875" bestFit="1" customWidth="1" min="23" max="23"/>
+    <col width="15.21875" bestFit="1" customWidth="1" min="24" max="24"/>
+    <col width="11.109375" bestFit="1" customWidth="1" min="25" max="25"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="16.21875" bestFit="1" customWidth="1" min="27" max="27"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="28" max="28"/>
+    <col width="13.21875" bestFit="1" customWidth="1" min="29" max="29"/>
+    <col width="13.77734375" bestFit="1" customWidth="1" min="30" max="30"/>
+    <col width="14.33203125" bestFit="1" customWidth="1" min="31" max="31"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="32" max="32"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11.88671875" bestFit="1" customWidth="1" min="35" max="35"/>
+    <col width="12.77734375" bestFit="1" customWidth="1" min="36" max="36"/>
+    <col width="20.109375" bestFit="1" customWidth="1" min="37" max="37"/>
+    <col width="12.21875" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="39" max="39"/>
+    <col width="16.21875" bestFit="1" customWidth="1" min="40" max="40"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="29">
-      <c r="A1" s="37" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>PERP (may)</t>
         </is>
       </c>
-      <c r="AA1" s="38" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>SPOT/ALPHA (may)</t>
         </is>
       </c>
-      <c r="AK1" s="39" t="inlineStr">
+      <c r="AK1" s="10" t="inlineStr">
         <is>
           <t>ON-CHAIN (ban tu dong)</t>
         </is>
       </c>
-      <c r="AN1" s="40" t="inlineStr">
+      <c r="AN1" s="11" t="inlineStr">
         <is>
           <t>MANUAL (operator)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="29">
-      <c r="A2" s="41" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>px_avg</t>
         </is>
       </c>
-      <c r="C2" s="41" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>ret_1d</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>vol_perp_usd</t>
         </is>
       </c>
-      <c r="E2" s="41" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>taker_buy_pct</t>
         </is>
       </c>
-      <c r="F2" s="41" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>f_avg</t>
         </is>
       </c>
-      <c r="G2" s="41" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>f_min</t>
         </is>
       </c>
-      <c r="H2" s="41" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>f_max</t>
         </is>
       </c>
-      <c r="I2" s="41" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>f_n</t>
         </is>
       </c>
-      <c r="J2" s="41" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>funding_regime</t>
         </is>
       </c>
-      <c r="K2" s="41" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>pin_streak</t>
         </is>
       </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>oi_usd</t>
         </is>
       </c>
-      <c r="M2" s="41" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>oi_vs_med14</t>
         </is>
       </c>
-      <c r="N2" s="41" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>oi_cycle_pos</t>
         </is>
       </c>
-      <c r="O2" s="41" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>lsr_pos_r</t>
         </is>
       </c>
-      <c r="P2" s="41" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>lsr_acc_r</t>
         </is>
       </c>
-      <c r="Q2" s="41" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>lsr_global_r</t>
         </is>
       </c>
-      <c r="R2" s="41" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr">
         <is>
           <t>div_raw</t>
         </is>
       </c>
-      <c r="S2" s="41" t="inlineStr">
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>div_avg3</t>
         </is>
       </c>
-      <c r="T2" s="41" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>glsr_slope_5d</t>
         </is>
       </c>
-      <c r="U2" s="41" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr">
         <is>
           <t>d_pos_3d</t>
         </is>
       </c>
-      <c r="V2" s="41" t="inlineStr">
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>d_acc_3d</t>
         </is>
       </c>
-      <c r="W2" s="41" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>signals_bullish</t>
         </is>
       </c>
-      <c r="X2" s="41" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>signals_suppress</t>
         </is>
       </c>
-      <c r="Y2" s="41" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>screen_rank</t>
         </is>
       </c>
-      <c r="Z2" s="41" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>data_bad</t>
         </is>
       </c>
-      <c r="AA2" s="42" t="inlineStr">
+      <c r="AA2" s="13" t="inlineStr">
         <is>
           <t>spot_venue</t>
         </is>
       </c>
-      <c r="AB2" s="42" t="inlineStr">
+      <c r="AB2" s="13" t="inlineStr">
         <is>
           <t>vol_spot_usd</t>
         </is>
       </c>
-      <c r="AC2" s="42" t="inlineStr">
+      <c r="AC2" s="13" t="inlineStr">
         <is>
           <t>taker_spot_pct</t>
         </is>
       </c>
-      <c r="AD2" s="42" t="inlineStr">
+      <c r="AD2" s="13" t="inlineStr">
         <is>
           <t>depth_bid2_usd</t>
         </is>
       </c>
-      <c r="AE2" s="42" t="inlineStr">
+      <c r="AE2" s="13" t="inlineStr">
         <is>
           <t>depth_ask2_usd</t>
         </is>
       </c>
-      <c r="AF2" s="42" t="inlineStr">
+      <c r="AF2" s="13" t="inlineStr">
         <is>
           <t>bid_wall_px</t>
         </is>
       </c>
-      <c r="AG2" s="42" t="inlineStr">
+      <c r="AG2" s="13" t="inlineStr">
         <is>
           <t>bid_wall_usd</t>
         </is>
       </c>
-      <c r="AH2" s="42" t="inlineStr">
+      <c r="AH2" s="13" t="inlineStr">
         <is>
           <t>ask_wall_px</t>
         </is>
       </c>
-      <c r="AI2" s="42" t="inlineStr">
+      <c r="AI2" s="13" t="inlineStr">
         <is>
           <t>ask_wall_usd</t>
         </is>
       </c>
-      <c r="AJ2" s="42" t="inlineStr">
+      <c r="AJ2" s="13" t="inlineStr">
         <is>
           <t>alpha_suspect</t>
         </is>
       </c>
-      <c r="AK2" s="43" t="inlineStr">
+      <c r="AK2" s="14" t="inlineStr">
         <is>
           <t>exch_balance_delta</t>
         </is>
       </c>
-      <c r="AL2" s="43" t="inlineStr">
+      <c r="AL2" s="14" t="inlineStr">
         <is>
           <t>wallet_activity</t>
         </is>
       </c>
-      <c r="AM2" s="43" t="inlineStr">
+      <c r="AM2" s="14" t="inlineStr">
         <is>
           <t>dominance_pct</t>
         </is>
       </c>
-      <c r="AN2" s="43" t="inlineStr">
+      <c r="AN2" s="14" t="inlineStr">
         <is>
           <t>note_operator</t>
         </is>
       </c>
-      <c r="AO2" s="43" t="inlineStr">
+      <c r="AO2" s="14" t="inlineStr">
         <is>
           <t>mm_note</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="44" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n">
+      <c r="B3" s="16" t="n">
         <v>0.0186562358117994</v>
       </c>
-      <c r="D3" s="46" t="n">
+      <c r="D3" s="17" t="n">
         <v>16584068.48426</v>
       </c>
-      <c r="E3" s="47" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.4780007889437288</v>
       </c>
-      <c r="F3" s="48" t="n">
+      <c r="F3" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G3" s="48" t="n">
+      <c r="G3" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H3" s="48" t="n">
+      <c r="H3" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I3" s="49" t="n">
+      <c r="I3" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K3" s="28" t="n">
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="46" t="n">
+      <c r="L3" s="17" t="n">
         <v>3099014.82334011</v>
       </c>
-      <c r="O3" s="51" t="n">
+      <c r="O3" s="22" t="n">
         <v>1.2677</v>
       </c>
-      <c r="P3" s="51" t="n">
+      <c r="P3" s="22" t="n">
         <v>1.7941</v>
       </c>
-      <c r="Q3" s="51" t="n">
+      <c r="Q3" s="22" t="n">
         <v>1.8563</v>
       </c>
-      <c r="R3" s="52">
+      <c r="R3" s="23">
         <f>IFERROR(O3/P3,"")</f>
         <v/>
       </c>
-      <c r="S3" s="28">
+      <c r="S3">
         <f>IFERROR(AVERAGE(R1:R3),"")</f>
         <v/>
       </c>
-      <c r="T3" s="28">
+      <c r="T3">
         <f>IFERROR(SLOPE(Q3:Q3,ROW(Q3:Q3)),"")</f>
         <v/>
       </c>
-      <c r="AA3" s="50" t="n"/>
-      <c r="AJ3" s="47">
+      <c r="AA3" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>223517</v>
+      </c>
+      <c r="AJ3" s="18">
         <f>IF(OR(AB3="",D3="",D3=0),"",AB3/D3)</f>
         <v/>
       </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Gate=0.2235M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n">
+      <c r="B4" s="16" t="n">
         <v>0.0155407362488524</v>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="24">
         <f>IFERROR(B4/B3-1,"")</f>
         <v/>
       </c>
-      <c r="D4" s="46" t="n">
+      <c r="D4" s="17" t="n">
         <v>16258105.08826</v>
       </c>
-      <c r="E4" s="47" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.4760134092685071</v>
       </c>
-      <c r="F4" s="48" t="n">
+      <c r="F4" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G4" s="48" t="n">
+      <c r="G4" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H4" s="48" t="n">
+      <c r="H4" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I4" s="49" t="n">
+      <c r="I4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J4" s="50" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="46" t="n">
+      <c r="L4" s="17" t="n">
         <v>2894341.86324902</v>
       </c>
-      <c r="M4" s="28" t="n">
+      <c r="M4" t="n">
         <v>0.9659</v>
       </c>
-      <c r="O4" s="51" t="n">
+      <c r="O4" s="22" t="n">
         <v>1.2383</v>
       </c>
-      <c r="P4" s="51" t="n">
+      <c r="P4" s="22" t="n">
         <v>1.6874</v>
       </c>
-      <c r="Q4" s="51" t="n">
+      <c r="Q4" s="22" t="n">
         <v>1.5491</v>
       </c>
-      <c r="R4" s="52">
+      <c r="R4" s="23">
         <f>IFERROR(O4/P4,"")</f>
         <v/>
       </c>
-      <c r="S4" s="28">
+      <c r="S4">
         <f>IFERROR(AVERAGE(R2:R4),"")</f>
         <v/>
       </c>
-      <c r="T4" s="28">
+      <c r="T4">
         <f>IFERROR(SLOPE(Q3:Q4,ROW(Q3:Q4)),"")</f>
         <v/>
       </c>
-      <c r="AA4" s="50" t="n"/>
-      <c r="AJ4" s="47">
+      <c r="AA4" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>261083</v>
+      </c>
+      <c r="AJ4" s="18">
         <f>IF(OR(AB4="",D4="",D4=0),"",AB4/D4)</f>
         <v/>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Gate=0.2611M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="16" t="n">
         <v>0.0154007227098661</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="24">
         <f>IFERROR(B5/B4-1,"")</f>
         <v/>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="17" t="n">
         <v>15289807.35174</v>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.4987639777670687</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.000333755</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H5" s="48" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.00175253</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L5" s="46" t="n">
+      <c r="L5" s="17" t="n">
         <v>3288740.32126068</v>
       </c>
-      <c r="M5" s="28" t="n">
+      <c r="M5" t="n">
         <v>1.0612</v>
       </c>
-      <c r="O5" s="51" t="n">
+      <c r="O5" s="22" t="n">
         <v>1.2157</v>
       </c>
-      <c r="P5" s="51" t="n">
+      <c r="P5" s="22" t="n">
         <v>1.3031</v>
       </c>
-      <c r="Q5" s="51" t="n">
+      <c r="Q5" s="22" t="n">
         <v>1.1839</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="23">
         <f>IFERROR(O5/P5,"")</f>
         <v/>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="23">
         <f>IFERROR(AVERAGE(R3:R5),"")</f>
         <v/>
       </c>
-      <c r="T5" s="28">
+      <c r="T5">
         <f>IFERROR(SLOPE(Q3:Q5,ROW(Q3:Q5)),"")</f>
         <v/>
       </c>
-      <c r="AA5" s="50" t="n"/>
-      <c r="AJ5" s="47">
+      <c r="AA5" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>1320492</v>
+      </c>
+      <c r="AJ5" s="18">
         <f>IF(OR(AB5="",D5="",D5=0),"",AB5/D5)</f>
         <v/>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Gate=1.3205M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="16" t="n">
         <v>0.0151692526652024</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="24">
         <f>IFERROR(B6/B5-1,"")</f>
         <v/>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="17" t="n">
         <v>9154051.07804</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.4793609303403439</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.0001978166666666</v>
       </c>
-      <c r="G6" s="48" t="n">
+      <c r="G6" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="19" t="n">
         <v>0.00062215</v>
       </c>
-      <c r="I6" s="49" t="n">
+      <c r="I6" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="50" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L6" s="46" t="n">
+      <c r="L6" s="17" t="n">
         <v>3368438.685</v>
       </c>
-      <c r="M6" s="28" t="n">
+      <c r="M6" t="n">
         <v>1.0547</v>
       </c>
-      <c r="O6" s="51" t="n">
+      <c r="O6" s="22" t="n">
         <v>1.6161</v>
       </c>
-      <c r="P6" s="51" t="n">
+      <c r="P6" s="22" t="n">
         <v>0.9992</v>
       </c>
-      <c r="Q6" s="51" t="n">
+      <c r="Q6" s="22" t="n">
         <v>0.9212</v>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="23">
         <f>IFERROR(O6/P6,"")</f>
         <v/>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="23">
         <f>IFERROR(AVERAGE(R4:R6),"")</f>
         <v/>
       </c>
-      <c r="T6" s="28">
+      <c r="T6">
         <f>IFERROR(SLOPE(Q3:Q6,ROW(Q3:Q6)),"")</f>
         <v/>
       </c>
-      <c r="U6" s="53">
+      <c r="U6" s="24">
         <f>IFERROR(O6/O3-1,"")</f>
         <v/>
       </c>
-      <c r="V6" s="53">
+      <c r="V6" s="24">
         <f>IFERROR(P6/P3-1,"")</f>
         <v/>
       </c>
-      <c r="AA6" s="50" t="n"/>
-      <c r="AJ6" s="47">
+      <c r="AA6" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1222066</v>
+      </c>
+      <c r="AJ6" s="18">
         <f>IF(OR(AB6="",D6="",D6=0),"",AB6/D6)</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Gate=1.2221M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="16" t="n">
         <v>0.0151713984335179</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="24">
         <f>IFERROR(B7/B6-1,"")</f>
         <v/>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="17" t="n">
         <v>8775938.510639999</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.4869234392252542</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.0001027616666666</v>
       </c>
-      <c r="G7" s="48" t="n">
+      <c r="G7" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="19" t="n">
         <v>0.00026516</v>
       </c>
-      <c r="I7" s="49" t="n">
+      <c r="I7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="50" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L7" s="46" t="n">
+      <c r="L7" s="17" t="n">
         <v>3822812.78385291</v>
       </c>
-      <c r="M7" s="28" t="n">
+      <c r="M7" t="n">
         <v>1.1624</v>
       </c>
-      <c r="O7" s="51" t="n">
+      <c r="O7" s="22" t="n">
         <v>1.6555</v>
       </c>
-      <c r="P7" s="51" t="n">
+      <c r="P7" s="22" t="n">
         <v>1.0342</v>
       </c>
-      <c r="Q7" s="51" t="n">
+      <c r="Q7" s="22" t="n">
         <v>0.9697</v>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="23">
         <f>IFERROR(O7/P7,"")</f>
         <v/>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="23">
         <f>IFERROR(AVERAGE(R5:R7),"")</f>
         <v/>
       </c>
-      <c r="T7" s="28">
+      <c r="T7">
         <f>IFERROR(SLOPE(Q3:Q7,ROW(Q3:Q7)),"")</f>
         <v/>
       </c>
-      <c r="U7" s="53">
+      <c r="U7" s="24">
         <f>IFERROR(O7/O4-1,"")</f>
         <v/>
       </c>
-      <c r="V7" s="53">
+      <c r="V7" s="24">
         <f>IFERROR(P7/P4-1,"")</f>
         <v/>
       </c>
-      <c r="AA7" s="50" t="n"/>
-      <c r="AJ7" s="47">
+      <c r="AA7" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>220426</v>
+      </c>
+      <c r="AJ7" s="18">
         <f>IF(OR(AB7="",D7="",D7=0),"",AB7/D7)</f>
         <v/>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Gate=0.2204M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="16" t="n">
         <v>0.0149669649761218</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="24">
         <f>IFERROR(B8/B7-1,"")</f>
         <v/>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="17" t="n">
         <v>3998636.20652</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.4896940602481673</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G8" s="48" t="n">
+      <c r="G8" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I8" s="49" t="n">
+      <c r="I8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="50" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="46" t="n">
+      <c r="L8" s="17" t="n">
         <v>4019035.35353</v>
       </c>
-      <c r="M8" s="28" t="n">
+      <c r="M8" t="n">
         <v>1.2074</v>
       </c>
-      <c r="O8" s="51" t="n">
+      <c r="O8" s="22" t="n">
         <v>1.6657</v>
       </c>
-      <c r="P8" s="51" t="n">
+      <c r="P8" s="22" t="n">
         <v>1.1739</v>
       </c>
-      <c r="Q8" s="51" t="n">
+      <c r="Q8" s="22" t="n">
         <v>1.1151</v>
       </c>
-      <c r="R8" s="52">
+      <c r="R8" s="23">
         <f>IFERROR(O8/P8,"")</f>
         <v/>
       </c>
-      <c r="S8" s="52">
+      <c r="S8" s="23">
         <f>IFERROR(AVERAGE(R6:R8),"")</f>
         <v/>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="23">
         <f>IFERROR(SLOPE(Q4:Q8,ROW(Q4:Q8)),"")</f>
         <v/>
       </c>
-      <c r="U8" s="53">
+      <c r="U8" s="24">
         <f>IFERROR(O8/O5-1,"")</f>
         <v/>
       </c>
-      <c r="V8" s="53">
+      <c r="V8" s="24">
         <f>IFERROR(P8/P5-1,"")</f>
         <v/>
       </c>
-      <c r="AA8" s="50" t="n"/>
-      <c r="AJ8" s="47">
+      <c r="AA8" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>379886</v>
+      </c>
+      <c r="AJ8" s="18">
         <f>IF(OR(AB8="",D8="",D8=0),"",AB8/D8)</f>
         <v/>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Gate=0.3799M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="16" t="n">
         <v>0.0149050859345661</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="24">
         <f>IFERROR(B9/B8-1,"")</f>
         <v/>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="17" t="n">
         <v>2234192.34128</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.5182033005451896</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.0001081583333333</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G9" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="19" t="n">
         <v>0.0002796</v>
       </c>
-      <c r="I9" s="49" t="n">
+      <c r="I9" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="50" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L9" s="46" t="n">
+      <c r="L9" s="17" t="n">
         <v>3919803.9201946</v>
       </c>
-      <c r="M9" s="28" t="n">
+      <c r="M9" t="n">
         <v>1.1637</v>
       </c>
-      <c r="O9" s="51" t="n">
+      <c r="O9" s="22" t="n">
         <v>1.7207</v>
       </c>
-      <c r="P9" s="51" t="n">
+      <c r="P9" s="22" t="n">
         <v>1.373</v>
       </c>
-      <c r="Q9" s="51" t="n">
+      <c r="Q9" s="22" t="n">
         <v>1.3793</v>
       </c>
-      <c r="R9" s="52">
+      <c r="R9" s="23">
         <f>IFERROR(O9/P9,"")</f>
         <v/>
       </c>
-      <c r="S9" s="52">
+      <c r="S9" s="23">
         <f>IFERROR(AVERAGE(R7:R9),"")</f>
         <v/>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="23">
         <f>IFERROR(SLOPE(Q5:Q9,ROW(Q5:Q9)),"")</f>
         <v/>
       </c>
-      <c r="U9" s="53">
+      <c r="U9" s="24">
         <f>IFERROR(O9/O6-1,"")</f>
         <v/>
       </c>
-      <c r="V9" s="53">
+      <c r="V9" s="24">
         <f>IFERROR(P9/P6-1,"")</f>
         <v/>
       </c>
-      <c r="AA9" s="50" t="n"/>
-      <c r="AJ9" s="47">
+      <c r="AA9" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>116210</v>
+      </c>
+      <c r="AJ9" s="18">
         <f>IF(OR(AB9="",D9="",D9=0),"",AB9/D9)</f>
         <v/>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Gate=0.1162M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="16" t="n">
         <v>0.0147307021595668</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="24">
         <f>IFERROR(B10/B9-1,"")</f>
         <v/>
       </c>
-      <c r="D10" s="46" t="n">
+      <c r="D10" s="17" t="n">
         <v>2039666.02208</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.5287559261604627</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="19" t="n">
         <v>7.325333333333333e-05</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="19" t="n">
         <v>0.00015766</v>
       </c>
-      <c r="I10" s="49" t="n">
+      <c r="I10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J10" s="50" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L10" s="46" t="n">
+      <c r="L10" s="17" t="n">
         <v>3610128.86241584</v>
       </c>
-      <c r="M10" s="28" t="n">
+      <c r="M10" t="n">
         <v>1.0346</v>
       </c>
-      <c r="O10" s="51" t="n">
+      <c r="O10" s="22" t="n">
         <v>1.6935</v>
       </c>
-      <c r="P10" s="51" t="n">
+      <c r="P10" s="22" t="n">
         <v>1.6788</v>
       </c>
-      <c r="Q10" s="51" t="n">
+      <c r="Q10" s="22" t="n">
         <v>1.7495</v>
       </c>
-      <c r="R10" s="52">
+      <c r="R10" s="23">
         <f>IFERROR(O10/P10,"")</f>
         <v/>
       </c>
-      <c r="S10" s="52">
+      <c r="S10" s="23">
         <f>IFERROR(AVERAGE(R8:R10),"")</f>
         <v/>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="23">
         <f>IFERROR(SLOPE(Q6:Q10,ROW(Q6:Q10)),"")</f>
         <v/>
       </c>
-      <c r="U10" s="53">
+      <c r="U10" s="24">
         <f>IFERROR(O10/O7-1,"")</f>
         <v/>
       </c>
-      <c r="V10" s="53">
+      <c r="V10" s="24">
         <f>IFERROR(P10/P7-1,"")</f>
         <v/>
       </c>
-      <c r="AA10" s="50" t="n"/>
-      <c r="AJ10" s="47">
+      <c r="AA10" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>121348</v>
+      </c>
+      <c r="AJ10" s="18">
         <f>IF(OR(AB10="",D10="",D10=0),"",AB10/D10)</f>
         <v/>
       </c>
-      <c r="AN10" s="50" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="AN10" s="21" t="inlineStr">
+        <is>
+          <t>Gate=0.1213M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="16" t="n">
         <v>0.0149165190488646</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="24">
         <f>IFERROR(B11/B10-1,"")</f>
         <v/>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="17" t="n">
         <v>1585348.52764</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.4834225092042596</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G11" s="48" t="n">
+      <c r="G11" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K11" s="28" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="46" t="n">
+      <c r="L11" s="17" t="n">
         <v>3703377.95163</v>
       </c>
-      <c r="M11" s="28" t="n">
+      <c r="M11" t="n">
         <v>1.0258</v>
       </c>
-      <c r="O11" s="51" t="n">
+      <c r="O11" s="22" t="n">
         <v>1.649</v>
       </c>
-      <c r="P11" s="51" t="n">
+      <c r="P11" s="22" t="n">
         <v>1.777</v>
       </c>
-      <c r="Q11" s="51" t="n">
+      <c r="Q11" s="22" t="n">
         <v>2.0139</v>
       </c>
-      <c r="R11" s="52">
+      <c r="R11" s="23">
         <f>IFERROR(O11/P11,"")</f>
         <v/>
       </c>
-      <c r="S11" s="52">
+      <c r="S11" s="23">
         <f>IFERROR(AVERAGE(R9:R11),"")</f>
         <v/>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="23">
         <f>IFERROR(SLOPE(Q7:Q11,ROW(Q7:Q11)),"")</f>
         <v/>
       </c>
-      <c r="U11" s="53">
+      <c r="U11" s="24">
         <f>IFERROR(O11/O8-1,"")</f>
         <v/>
       </c>
-      <c r="V11" s="53">
+      <c r="V11" s="24">
         <f>IFERROR(P11/P8-1,"")</f>
         <v/>
       </c>
-      <c r="W11" s="50" t="n"/>
-      <c r="AA11" s="50" t="n"/>
-      <c r="AJ11" s="47">
+      <c r="W11" s="21" t="n"/>
+      <c r="AA11" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>85543</v>
+      </c>
+      <c r="AJ11" s="18">
         <f>IF(OR(AB11="",D11="",D11=0),"",AB11/D11)</f>
         <v/>
       </c>
-      <c r="AN11" s="50" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="AN11" s="21" t="inlineStr">
+        <is>
+          <t>Gate=0.0855M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="16" t="n">
         <v>0.015688121367546</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="24">
         <f>IFERROR(B12/B11-1,"")</f>
         <v/>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="17" t="n">
         <v>3092893.51746</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.4726014443408847</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="19" t="n">
         <v>0.0002229483333333</v>
       </c>
-      <c r="G12" s="48" t="n">
+      <c r="G12" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="19" t="n">
         <v>0.0003584</v>
       </c>
-      <c r="I12" s="49" t="n">
+      <c r="I12" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="17" t="n">
         <v>3785021.2347584</v>
       </c>
-      <c r="M12" s="28" t="n">
+      <c r="M12" t="n">
         <v>1.0351</v>
       </c>
-      <c r="O12" s="51" t="n">
+      <c r="O12" s="22" t="n">
         <v>1.6521</v>
       </c>
-      <c r="P12" s="51" t="n">
+      <c r="P12" s="22" t="n">
         <v>1.8074</v>
       </c>
-      <c r="Q12" s="51" t="n">
+      <c r="Q12" s="22" t="n">
         <v>2.1027</v>
       </c>
-      <c r="R12" s="52">
+      <c r="R12" s="23">
         <f>IFERROR(O12/P12,"")</f>
         <v/>
       </c>
-      <c r="S12" s="52">
+      <c r="S12" s="23">
         <f>IFERROR(AVERAGE(R10:R12),"")</f>
         <v/>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="23">
         <f>IFERROR(SLOPE(Q8:Q12,ROW(Q8:Q12)),"")</f>
         <v/>
       </c>
-      <c r="U12" s="53">
+      <c r="U12" s="24">
         <f>IFERROR(O12/O9-1,"")</f>
         <v/>
       </c>
-      <c r="V12" s="53">
+      <c r="V12" s="24">
         <f>IFERROR(P12/P9-1,"")</f>
         <v/>
       </c>
-      <c r="W12" s="50" t="n"/>
-      <c r="AA12" s="50" t="n"/>
-      <c r="AJ12" s="47">
+      <c r="W12" s="21" t="n"/>
+      <c r="AA12" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>137097</v>
+      </c>
+      <c r="AJ12" s="18">
         <f>IF(OR(AB12="",D12="",D12=0),"",AB12/D12)</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Gate=0.1371M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="16" t="n">
         <v>0.0149643088402328</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="24">
         <f>IFERROR(B13/B12-1,"")</f>
         <v/>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="17" t="n">
         <v>5087129.7194</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.4201435632151012</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="19" t="n">
         <v>0.00028204</v>
       </c>
-      <c r="G13" s="48" t="n">
+      <c r="G13" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H13" s="48" t="n">
+      <c r="H13" s="19" t="n">
         <v>0.00046765</v>
       </c>
-      <c r="I13" s="49" t="n">
+      <c r="I13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="17" t="n">
         <v>4039535.29168</v>
       </c>
-      <c r="M13" s="28" t="n">
+      <c r="M13" t="n">
         <v>1.0908</v>
       </c>
-      <c r="O13" s="51" t="n">
+      <c r="O13" s="22" t="n">
         <v>1.6568</v>
       </c>
-      <c r="P13" s="51" t="n">
+      <c r="P13" s="22" t="n">
         <v>1.8835</v>
       </c>
-      <c r="Q13" s="51" t="n">
+      <c r="Q13" s="22" t="n">
         <v>2.1358</v>
       </c>
-      <c r="R13" s="52">
+      <c r="R13" s="23">
         <f>IFERROR(O13/P13,"")</f>
         <v/>
       </c>
-      <c r="S13" s="52">
+      <c r="S13" s="23">
         <f>IFERROR(AVERAGE(R11:R13),"")</f>
         <v/>
       </c>
-      <c r="T13" s="52">
+      <c r="T13" s="23">
         <f>IFERROR(SLOPE(Q9:Q13,ROW(Q9:Q13)),"")</f>
         <v/>
       </c>
-      <c r="U13" s="53">
+      <c r="U13" s="24">
         <f>IFERROR(O13/O10-1,"")</f>
         <v/>
       </c>
-      <c r="V13" s="53">
+      <c r="V13" s="24">
         <f>IFERROR(P13/P10-1,"")</f>
         <v/>
       </c>
-      <c r="W13" s="50" t="n"/>
-      <c r="AA13" s="50" t="n"/>
-      <c r="AJ13" s="47">
+      <c r="W13" s="21" t="n"/>
+      <c r="AA13" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>356547</v>
+      </c>
+      <c r="AJ13" s="18">
         <f>IF(OR(AB13="",D13="",D13=0),"",AB13/D13)</f>
         <v/>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Gate=0.3565M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="16" t="n">
         <v>0.0156643305572706</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="24">
         <f>IFERROR(B14/B13-1,"")</f>
         <v/>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="17" t="n">
         <v>7737632.26554</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.4939444565350427</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="19" t="n">
         <v>0.0001749233333333</v>
       </c>
-      <c r="G14" s="48" t="n">
+      <c r="G14" s="19" t="n">
         <v>5.781e-05</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="19" t="n">
         <v>0.00023305</v>
       </c>
-      <c r="I14" s="49" t="n">
+      <c r="I14" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L14" s="46" t="n">
+      <c r="L14" s="17" t="n">
         <v>3648049.4052</v>
       </c>
-      <c r="M14" s="28" t="n">
+      <c r="M14" t="n">
         <v>0.9925</v>
       </c>
-      <c r="O14" s="51" t="n">
+      <c r="O14" s="22" t="n">
         <v>1.7032</v>
       </c>
-      <c r="P14" s="51" t="n">
+      <c r="P14" s="22" t="n">
         <v>1.694</v>
       </c>
-      <c r="Q14" s="51" t="n">
+      <c r="Q14" s="22" t="n">
         <v>1.7571</v>
       </c>
-      <c r="R14" s="52">
+      <c r="R14" s="23">
         <f>IFERROR(O14/P14,"")</f>
         <v/>
       </c>
-      <c r="S14" s="52">
+      <c r="S14" s="23">
         <f>IFERROR(AVERAGE(R12:R14),"")</f>
         <v/>
       </c>
-      <c r="T14" s="52">
+      <c r="T14" s="23">
         <f>IFERROR(SLOPE(Q10:Q14,ROW(Q10:Q14)),"")</f>
         <v/>
       </c>
-      <c r="U14" s="53">
+      <c r="U14" s="24">
         <f>IFERROR(O14/O11-1,"")</f>
         <v/>
       </c>
-      <c r="V14" s="53">
+      <c r="V14" s="24">
         <f>IFERROR(P14/P11-1,"")</f>
         <v/>
       </c>
-      <c r="W14" s="50" t="n"/>
-      <c r="AA14" s="50" t="n"/>
-      <c r="AJ14" s="47">
+      <c r="W14" s="21" t="n"/>
+      <c r="AA14" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>123180</v>
+      </c>
+      <c r="AJ14" s="18">
         <f>IF(OR(AB14="",D14="",D14=0),"",AB14/D14)</f>
         <v/>
       </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Gate=0.1232M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B15" s="45" t="n">
+      <c r="B15" s="16" t="n">
         <v>0.0150097239324522</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="24">
         <f>IFERROR(B15/B14-1,"")</f>
         <v/>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="17" t="n">
         <v>5876711.16144</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.4754047375273049</v>
       </c>
-      <c r="F15" s="48" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.00016166</v>
       </c>
-      <c r="G15" s="48" t="n">
+      <c r="G15" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="19" t="n">
         <v>0.00027553</v>
       </c>
-      <c r="I15" s="49" t="n">
+      <c r="I15" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L15" s="46" t="n">
+      <c r="L15" s="17" t="n">
         <v>4181571.77787</v>
       </c>
-      <c r="M15" s="28" t="n">
+      <c r="M15" t="n">
         <v>1.1291</v>
       </c>
-      <c r="O15" s="51" t="n">
+      <c r="O15" s="22" t="n">
         <v>1.7488</v>
       </c>
-      <c r="P15" s="51" t="n">
+      <c r="P15" s="22" t="n">
         <v>1.2676</v>
       </c>
-      <c r="Q15" s="51" t="n">
+      <c r="Q15" s="22" t="n">
         <v>1.2427</v>
       </c>
-      <c r="R15" s="52">
+      <c r="R15" s="23">
         <f>IFERROR(O15/P15,"")</f>
         <v/>
       </c>
-      <c r="S15" s="52">
+      <c r="S15" s="23">
         <f>IFERROR(AVERAGE(R13:R15),"")</f>
         <v/>
       </c>
-      <c r="T15" s="52">
+      <c r="T15" s="23">
         <f>IFERROR(SLOPE(Q11:Q15,ROW(Q11:Q15)),"")</f>
         <v/>
       </c>
-      <c r="U15" s="53">
+      <c r="U15" s="24">
         <f>IFERROR(O15/O12-1,"")</f>
         <v/>
       </c>
-      <c r="V15" s="53">
+      <c r="V15" s="24">
         <f>IFERROR(P15/P12-1,"")</f>
         <v/>
       </c>
-      <c r="W15" s="50" t="n"/>
-      <c r="AA15" s="50" t="n"/>
-      <c r="AJ15" s="47">
+      <c r="W15" s="21" t="n"/>
+      <c r="AA15" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>333231</v>
+      </c>
+      <c r="AJ15" s="18">
         <f>IF(OR(AB15="",D15="",D15=0),"",AB15/D15)</f>
         <v/>
       </c>
-      <c r="AL15" s="50" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="AL15" s="21" t="n"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Gate=0.3332M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="16" t="n">
         <v>0.0152035500639097</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="24">
         <f>IFERROR(B16/B15-1,"")</f>
         <v/>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="17" t="n">
         <v>2231442.34452</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="18" t="n">
         <v>0.4851628254050874</v>
       </c>
-      <c r="F16" s="48" t="n">
+      <c r="F16" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G16" s="48" t="n">
+      <c r="G16" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="I16" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="46" t="n">
+      <c r="L16" s="17" t="n">
         <v>3966026.87273247</v>
       </c>
-      <c r="M16" s="28" t="n">
+      <c r="M16" t="n">
         <v>1.0592</v>
       </c>
-      <c r="O16" s="51" t="n">
+      <c r="O16" s="22" t="n">
         <v>1.8127</v>
       </c>
-      <c r="P16" s="51" t="n">
+      <c r="P16" s="22" t="n">
         <v>1.2889</v>
       </c>
-      <c r="Q16" s="51" t="n">
+      <c r="Q16" s="22" t="n">
         <v>1.2168</v>
       </c>
-      <c r="R16" s="52">
+      <c r="R16" s="23">
         <f>IFERROR(O16/P16,"")</f>
         <v/>
       </c>
-      <c r="S16" s="52">
+      <c r="S16" s="23">
         <f>IFERROR(AVERAGE(R14:R16),"")</f>
         <v/>
       </c>
-      <c r="T16" s="52">
+      <c r="T16" s="23">
         <f>IFERROR(SLOPE(Q12:Q16,ROW(Q12:Q16)),"")</f>
         <v/>
       </c>
-      <c r="U16" s="53">
+      <c r="U16" s="24">
         <f>IFERROR(O16/O13-1,"")</f>
         <v/>
       </c>
-      <c r="V16" s="53">
+      <c r="V16" s="24">
         <f>IFERROR(P16/P13-1,"")</f>
         <v/>
       </c>
-      <c r="W16" s="50" t="n"/>
-      <c r="AA16" s="50" t="n"/>
-      <c r="AJ16" s="47">
+      <c r="W16" s="21" t="n"/>
+      <c r="AA16" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>78360</v>
+      </c>
+      <c r="AJ16" s="18">
         <f>IF(OR(AB16="",D16="",D16=0),"",AB16/D16)</f>
         <v/>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="29">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Gate=0.0784M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n">
+      <c r="B17" s="16" t="n">
         <v>0.0153643680398057</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="24">
         <f>IFERROR(B17/B16-1,"")</f>
         <v/>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="17" t="n">
         <v>15102738.57204</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="18" t="n">
         <v>0.5092075492693098</v>
       </c>
-      <c r="F17" s="48" t="n">
+      <c r="F17" s="19" t="n">
         <v>0.0001101583333333</v>
       </c>
-      <c r="G17" s="48" t="n">
+      <c r="G17" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="19" t="n">
         <v>0.00041095</v>
       </c>
-      <c r="I17" s="49" t="n">
+      <c r="I17" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L17" s="46" t="n">
+      <c r="L17" s="17" t="n">
         <v>4045709.36016</v>
       </c>
-      <c r="M17" s="54" t="n">
+      <c r="M17" s="25" t="n">
         <v>1.0636</v>
       </c>
-      <c r="O17" s="51" t="n">
+      <c r="O17" s="22" t="n">
         <v>1.8834</v>
       </c>
-      <c r="P17" s="51" t="n">
+      <c r="P17" s="22" t="n">
         <v>1.4618</v>
       </c>
-      <c r="Q17" s="51" t="n">
+      <c r="Q17" s="22" t="n">
         <v>1.4814</v>
       </c>
-      <c r="R17" s="52">
+      <c r="R17" s="23">
         <f>IFERROR(O17/P17,"")</f>
         <v/>
       </c>
-      <c r="S17" s="52">
+      <c r="S17" s="23">
         <f>IFERROR(AVERAGE(R15:R17),"")</f>
         <v/>
       </c>
-      <c r="T17" s="52">
+      <c r="T17" s="23">
         <f>IFERROR(SLOPE(Q13:Q17,ROW(Q13:Q17)),"")</f>
         <v/>
       </c>
-      <c r="U17" s="53">
+      <c r="U17" s="24">
         <f>IFERROR(O17/O14-1,"")</f>
         <v/>
       </c>
-      <c r="V17" s="53">
+      <c r="V17" s="24">
         <f>IFERROR(P17/P14-1,"")</f>
         <v/>
       </c>
-      <c r="W17" s="50" t="n"/>
-      <c r="AA17" s="50" t="n"/>
-      <c r="AJ17" s="47">
+      <c r="W17" s="21" t="n"/>
+      <c r="AA17" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>88198</v>
+      </c>
+      <c r="AJ17" s="18">
         <f>IF(OR(AB17="",D17="",D17=0),"",AB17/D17)</f>
         <v/>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="29">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Gate=0.0882M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="B18" s="45" t="n">
+      <c r="B18" s="16" t="n">
         <v>0.0154595186864351</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="24">
         <f>IFERROR(B18/B17-1,"")</f>
         <v/>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="17" t="n">
         <v>3673663.97688</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="18" t="n">
         <v>0.4874717761027368</v>
       </c>
-      <c r="F18" s="48" t="n">
+      <c r="F18" s="19" t="n">
         <v>0.0001210316666666</v>
       </c>
-      <c r="G18" s="48" t="n">
+      <c r="G18" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H18" s="48" t="n">
+      <c r="H18" s="19" t="n">
         <v>0.0002721</v>
       </c>
-      <c r="I18" s="49" t="n">
+      <c r="I18" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="17" t="n">
         <v>6125332.04553</v>
       </c>
-      <c r="M18" s="54" t="n">
+      <c r="M18" s="25" t="n">
         <v>1.5822</v>
       </c>
-      <c r="O18" s="51" t="n">
+      <c r="O18" s="22" t="n">
         <v>1.4154</v>
       </c>
-      <c r="P18" s="51" t="n">
+      <c r="P18" s="22" t="n">
         <v>1.5615</v>
       </c>
-      <c r="Q18" s="51" t="n">
+      <c r="Q18" s="22" t="n">
         <v>1.4667</v>
       </c>
-      <c r="R18" s="52">
+      <c r="R18" s="23">
         <f>IFERROR(O18/P18,"")</f>
         <v/>
       </c>
-      <c r="S18" s="52">
+      <c r="S18" s="23">
         <f>IFERROR(AVERAGE(R16:R18),"")</f>
         <v/>
       </c>
-      <c r="T18" s="52">
+      <c r="T18" s="23">
         <f>IFERROR(SLOPE(Q14:Q18,ROW(Q14:Q18)),"")</f>
         <v/>
       </c>
-      <c r="U18" s="53">
+      <c r="U18" s="24">
         <f>IFERROR(O18/O15-1,"")</f>
         <v/>
       </c>
-      <c r="V18" s="53">
+      <c r="V18" s="24">
         <f>IFERROR(P18/P15-1,"")</f>
         <v/>
       </c>
-      <c r="W18" s="50" t="n"/>
-      <c r="AA18" s="50" t="n"/>
-      <c r="AJ18" s="47">
+      <c r="W18" s="21" t="n"/>
+      <c r="AA18" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>91266</v>
+      </c>
+      <c r="AJ18" s="18">
         <f>IF(OR(AB18="",D18="",D18=0),"",AB18/D18)</f>
         <v/>
       </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="29">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Gate=0.0913M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B19" s="45" t="n">
+      <c r="B19" s="16" t="n">
         <v>0.0169219684626267</v>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="24">
         <f>IFERROR(B19/B18-1,"")</f>
         <v/>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="17" t="n">
         <v>24678006.63704</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="18" t="n">
         <v>0.4971711271568416</v>
       </c>
-      <c r="F19" s="48" t="n">
+      <c r="F19" s="19" t="n">
         <v>0.0002538166666666</v>
       </c>
-      <c r="G19" s="48" t="n">
+      <c r="G19" s="19" t="n">
         <v>0.00011075</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="19" t="n">
         <v>0.00035747</v>
       </c>
-      <c r="I19" s="49" t="n">
+      <c r="I19" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="50" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L19" s="46" t="n">
+      <c r="L19" s="17" t="n">
         <v>6122375.81934</v>
       </c>
-      <c r="M19" s="54" t="n">
+      <c r="M19" s="25" t="n">
         <v>1.5528</v>
       </c>
-      <c r="O19" s="51" t="n">
+      <c r="O19" s="22" t="n">
         <v>1.4507</v>
       </c>
-      <c r="P19" s="51" t="n">
+      <c r="P19" s="22" t="n">
         <v>1.5628</v>
       </c>
-      <c r="Q19" s="51" t="n">
+      <c r="Q19" s="22" t="n">
         <v>1.4969</v>
       </c>
-      <c r="R19" s="52">
+      <c r="R19" s="23">
         <f>IFERROR(O19/P19,"")</f>
         <v/>
       </c>
-      <c r="S19" s="52">
+      <c r="S19" s="23">
         <f>IFERROR(AVERAGE(R17:R19),"")</f>
         <v/>
       </c>
-      <c r="T19" s="52">
+      <c r="T19" s="23">
         <f>IFERROR(SLOPE(Q15:Q19,ROW(Q15:Q19)),"")</f>
         <v/>
       </c>
-      <c r="U19" s="53">
+      <c r="U19" s="24">
         <f>IFERROR(O19/O16-1,"")</f>
         <v/>
       </c>
-      <c r="V19" s="53">
+      <c r="V19" s="24">
         <f>IFERROR(P19/P16-1,"")</f>
         <v/>
       </c>
-      <c r="W19" s="50" t="n"/>
-      <c r="AA19" s="50" t="n"/>
-      <c r="AJ19" s="47">
+      <c r="W19" s="21" t="n"/>
+      <c r="AA19" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>119616</v>
+      </c>
+      <c r="AJ19" s="18">
         <f>IF(OR(AB19="",D19="",D19=0),"",AB19/D19)</f>
         <v/>
       </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="29">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Gate=0.1196M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n">
+      <c r="B20" s="16" t="n">
         <v>0.0171765164045538</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="24">
         <f>IFERROR(B20/B19-1,"")</f>
         <v/>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="17" t="n">
         <v>8491991.76338</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="18" t="n">
         <v>0.4962701448405486</v>
       </c>
-      <c r="F20" s="48" t="n">
+      <c r="F20" s="19" t="n">
         <v>0.0001529483333333</v>
       </c>
-      <c r="G20" s="48" t="n">
+      <c r="G20" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="19" t="n">
         <v>0.00037102</v>
       </c>
-      <c r="I20" s="49" t="n">
+      <c r="I20" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L20" s="46" t="n">
+      <c r="L20" s="17" t="n">
         <v>7178207.5735595</v>
       </c>
-      <c r="M20" s="54" t="n">
+      <c r="M20" s="25" t="n">
         <v>1.7979</v>
       </c>
-      <c r="O20" s="51" t="n">
+      <c r="O20" s="22" t="n">
         <v>1.4419</v>
       </c>
-      <c r="P20" s="51" t="n">
+      <c r="P20" s="22" t="n">
         <v>1.2696</v>
       </c>
-      <c r="Q20" s="51" t="n">
+      <c r="Q20" s="22" t="n">
         <v>1.2841</v>
       </c>
-      <c r="R20" s="52">
+      <c r="R20" s="23">
         <f>IFERROR(O20/P20,"")</f>
         <v/>
       </c>
-      <c r="S20" s="52">
+      <c r="S20" s="23">
         <f>IFERROR(AVERAGE(R18:R20),"")</f>
         <v/>
       </c>
-      <c r="T20" s="52">
+      <c r="T20" s="23">
         <f>IFERROR(SLOPE(Q16:Q20,ROW(Q16:Q20)),"")</f>
         <v/>
       </c>
-      <c r="U20" s="53">
+      <c r="U20" s="24">
         <f>IFERROR(O20/O17-1,"")</f>
         <v/>
       </c>
-      <c r="V20" s="53">
+      <c r="V20" s="24">
         <f>IFERROR(P20/P17-1,"")</f>
         <v/>
       </c>
-      <c r="AA20" s="50" t="n"/>
-      <c r="AJ20" s="47">
+      <c r="AA20" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>75888</v>
+      </c>
+      <c r="AJ20" s="18">
         <f>IF(OR(AB20="",D20="",D20=0),"",AB20/D20)</f>
         <v/>
       </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="29">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Gate=0.0759M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="B21" s="45" t="n">
+      <c r="B21" s="16" t="n">
         <v>0.0173322098095639</v>
       </c>
-      <c r="C21" s="53">
+      <c r="C21" s="24">
         <f>IFERROR(B21/B20-1,"")</f>
         <v/>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="17" t="n">
         <v>16647813.36078</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="18" t="n">
         <v>0.4870963550740638</v>
       </c>
-      <c r="F21" s="48" t="n">
+      <c r="F21" s="19" t="n">
         <v>0.0001377833333333</v>
       </c>
-      <c r="G21" s="48" t="n">
+      <c r="G21" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H21" s="48" t="n">
+      <c r="H21" s="19" t="n">
         <v>0.00054775</v>
       </c>
-      <c r="I21" s="49" t="n">
+      <c r="I21" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L21" s="46" t="n">
+      <c r="L21" s="17" t="n">
         <v>6982667.8074</v>
       </c>
-      <c r="M21" s="54" t="n">
+      <c r="M21" s="25" t="n">
         <v>1.733</v>
       </c>
-      <c r="O21" s="51" t="n">
+      <c r="O21" s="22" t="n">
         <v>1.4585</v>
       </c>
-      <c r="P21" s="51" t="n">
+      <c r="P21" s="22" t="n">
         <v>1.2262</v>
       </c>
-      <c r="Q21" s="51" t="n">
+      <c r="Q21" s="22" t="n">
         <v>1.1753</v>
       </c>
-      <c r="R21" s="52">
+      <c r="R21" s="23">
         <f>IFERROR(O21/P21,"")</f>
         <v/>
       </c>
-      <c r="S21" s="52">
+      <c r="S21" s="23">
         <f>IFERROR(AVERAGE(R19:R21),"")</f>
         <v/>
       </c>
-      <c r="T21" s="52">
+      <c r="T21" s="23">
         <f>IFERROR(SLOPE(Q17:Q21,ROW(Q17:Q21)),"")</f>
         <v/>
       </c>
-      <c r="U21" s="53">
+      <c r="U21" s="24">
         <f>IFERROR(O21/O18-1,"")</f>
         <v/>
       </c>
-      <c r="V21" s="53">
+      <c r="V21" s="24">
         <f>IFERROR(P21/P18-1,"")</f>
         <v/>
       </c>
-      <c r="AA21" s="50" t="n"/>
-      <c r="AJ21" s="47">
+      <c r="AA21" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>77524</v>
+      </c>
+      <c r="AJ21" s="18">
         <f>IF(OR(AB21="",D21="",D21=0),"",AB21/D21)</f>
         <v/>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="29">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Gate=0.0775M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B22" s="45" t="n">
+      <c r="B22" s="16" t="n">
         <v>0.0158338033902253</v>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="24">
         <f>IFERROR(B22/B21-1,"")</f>
         <v/>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="17" t="n">
         <v>7550669.74948</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="18" t="n">
         <v>0.4496955742141414</v>
       </c>
-      <c r="F22" s="48" t="n">
+      <c r="F22" s="19" t="n">
         <v>0.0001454166666666</v>
       </c>
-      <c r="G22" s="48" t="n">
+      <c r="G22" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="19" t="n">
         <v>0.00048538</v>
       </c>
-      <c r="I22" s="49" t="n">
+      <c r="I22" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L22" s="46" t="n">
+      <c r="L22" s="17" t="n">
         <v>4702280.4471575</v>
       </c>
-      <c r="M22" s="54" t="n">
+      <c r="M22" s="25" t="n">
         <v>1.1632</v>
       </c>
-      <c r="O22" s="51" t="n">
+      <c r="O22" s="22" t="n">
         <v>1.8937</v>
       </c>
-      <c r="P22" s="51" t="n">
+      <c r="P22" s="22" t="n">
         <v>1.1349</v>
       </c>
-      <c r="Q22" s="51" t="n">
+      <c r="Q22" s="22" t="n">
         <v>1.0803</v>
       </c>
-      <c r="R22" s="52">
+      <c r="R22" s="23">
         <f>IFERROR(O22/P22,"")</f>
         <v/>
       </c>
-      <c r="S22" s="52">
+      <c r="S22" s="23">
         <f>IFERROR(AVERAGE(R20:R22),"")</f>
         <v/>
       </c>
-      <c r="T22" s="52">
+      <c r="T22" s="23">
         <f>IFERROR(SLOPE(Q18:Q22,ROW(Q18:Q22)),"")</f>
         <v/>
       </c>
-      <c r="U22" s="53">
+      <c r="U22" s="24">
         <f>IFERROR(O22/O19-1,"")</f>
         <v/>
       </c>
-      <c r="V22" s="53">
+      <c r="V22" s="24">
         <f>IFERROR(P22/P19-1,"")</f>
         <v/>
       </c>
-      <c r="AA22" s="50" t="n"/>
-      <c r="AJ22" s="47">
+      <c r="AA22" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>1687010</v>
+      </c>
+      <c r="AJ22" s="18">
         <f>IF(OR(AB22="",D22="",D22=0),"",AB22/D22)</f>
         <v/>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="29">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Gate=0.1552M | DEX_BSC(PancakeSwap)=1.5318M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="B23" s="45" t="n">
+      <c r="B23" s="16" t="n">
         <v>0.0150939456764887</v>
       </c>
-      <c r="C23" s="53">
+      <c r="C23" s="24">
         <f>IFERROR(B23/B22-1,"")</f>
         <v/>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="17" t="n">
         <v>1919723.54124</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="18" t="n">
         <v>0.4756811771186703</v>
       </c>
-      <c r="F23" s="48" t="n">
+      <c r="F23" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G23" s="48" t="n">
+      <c r="G23" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H23" s="48" t="n">
+      <c r="H23" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I23" s="49" t="n">
+      <c r="I23" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K23" s="28" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="46" t="n">
+      <c r="L23" s="17" t="n">
         <v>3924816.43765718</v>
       </c>
-      <c r="M23" s="54" t="n">
+      <c r="M23" s="25" t="n">
         <v>0.9709</v>
       </c>
-      <c r="O23" s="51" t="n">
+      <c r="O23" s="22" t="n">
         <v>1.9359</v>
       </c>
-      <c r="P23" s="51" t="n">
+      <c r="P23" s="22" t="n">
         <v>1.2272</v>
       </c>
-      <c r="Q23" s="51" t="n">
+      <c r="Q23" s="22" t="n">
         <v>1.1482</v>
       </c>
-      <c r="R23" s="52">
+      <c r="R23" s="23">
         <f>IFERROR(O23/P23,"")</f>
         <v/>
       </c>
-      <c r="S23" s="52">
+      <c r="S23" s="23">
         <f>IFERROR(AVERAGE(R21:R23),"")</f>
         <v/>
       </c>
-      <c r="T23" s="52">
+      <c r="T23" s="23">
         <f>IFERROR(SLOPE(Q19:Q23,ROW(Q19:Q23)),"")</f>
         <v/>
       </c>
-      <c r="U23" s="53">
+      <c r="U23" s="24">
         <f>IFERROR(O23/O20-1,"")</f>
         <v/>
       </c>
-      <c r="V23" s="53">
+      <c r="V23" s="24">
         <f>IFERROR(P23/P20-1,"")</f>
         <v/>
       </c>
-      <c r="AA23" s="50" t="n"/>
-      <c r="AJ23" s="47">
+      <c r="AA23" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>657484</v>
+      </c>
+      <c r="AJ23" s="18">
         <f>IF(OR(AB23="",D23="",D23=0),"",AB23/D23)</f>
         <v/>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="29">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Gate=0.0942M | DEX_BSC(PancakeSwap)=0.5633M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n">
+      <c r="B24" s="16" t="n">
         <v>0.015139866343385</v>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="24">
         <f>IFERROR(B24/B23-1,"")</f>
         <v/>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="17" t="n">
         <v>1713045.74842</v>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="18" t="n">
         <v>0.5459623019441526</v>
       </c>
-      <c r="F24" s="48" t="n">
+      <c r="F24" s="19" t="n">
         <v>6.360166666666667e-05</v>
       </c>
-      <c r="G24" s="48" t="n">
+      <c r="G24" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H24" s="48" t="n">
+      <c r="H24" s="19" t="n">
         <v>0.00013161</v>
       </c>
-      <c r="I24" s="49" t="n">
+      <c r="I24" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L24" s="46" t="n">
+      <c r="L24" s="17" t="n">
         <v>3839507.25819608</v>
       </c>
-      <c r="M24" s="54" t="n">
+      <c r="M24" s="25" t="n">
         <v>0.9498</v>
       </c>
-      <c r="O24" s="51" t="n">
+      <c r="O24" s="22" t="n">
         <v>1.9084</v>
       </c>
-      <c r="P24" s="51" t="n">
+      <c r="P24" s="22" t="n">
         <v>1.5846</v>
       </c>
-      <c r="Q24" s="51" t="n">
+      <c r="Q24" s="22" t="n">
         <v>1.4994</v>
       </c>
-      <c r="R24" s="52">
+      <c r="R24" s="23">
         <f>IFERROR(O24/P24,"")</f>
         <v/>
       </c>
-      <c r="S24" s="52">
+      <c r="S24" s="23">
         <f>IFERROR(AVERAGE(R22:R24),"")</f>
         <v/>
       </c>
-      <c r="T24" s="52">
+      <c r="T24" s="23">
         <f>IFERROR(SLOPE(Q20:Q24,ROW(Q20:Q24)),"")</f>
         <v/>
       </c>
-      <c r="U24" s="53">
+      <c r="U24" s="24">
         <f>IFERROR(O24/O21-1,"")</f>
         <v/>
       </c>
-      <c r="V24" s="53">
+      <c r="V24" s="24">
         <f>IFERROR(P24/P21-1,"")</f>
         <v/>
       </c>
-      <c r="AA24" s="50" t="n"/>
-      <c r="AJ24" s="47">
+      <c r="AA24" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>482966</v>
+      </c>
+      <c r="AJ24" s="18">
         <f>IF(OR(AB24="",D24="",D24=0),"",AB24/D24)</f>
         <v/>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="29">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Gate=0.0287M | DEX_BSC(PancakeSwap)=0.4543M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n">
+      <c r="B25" s="16" t="n">
         <v>0.0179970625217425</v>
       </c>
-      <c r="C25" s="53">
+      <c r="C25" s="24">
         <f>IFERROR(B25/B24-1,"")</f>
         <v/>
       </c>
-      <c r="D25" s="46" t="n">
+      <c r="D25" s="17" t="n">
         <v>167259563.39932</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="18" t="n">
         <v>0.4890935881891488</v>
       </c>
-      <c r="F25" s="48" t="n">
+      <c r="F25" s="19" t="n">
         <v>0.0002468083333333</v>
       </c>
-      <c r="G25" s="48" t="n">
+      <c r="G25" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H25" s="19" t="n">
         <v>0.00036813</v>
       </c>
-      <c r="I25" s="49" t="n">
+      <c r="I25" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L25" s="46" t="n">
+      <c r="L25" s="17" t="n">
         <v>3946003.54422922</v>
       </c>
-      <c r="M25" s="54" t="n">
+      <c r="M25" s="25" t="n">
         <v>0.9761</v>
       </c>
-      <c r="O25" s="51" t="n">
+      <c r="O25" s="22" t="n">
         <v>1.9113</v>
       </c>
-      <c r="P25" s="51" t="n">
+      <c r="P25" s="22" t="n">
         <v>1.7012</v>
       </c>
-      <c r="Q25" s="51" t="n">
+      <c r="Q25" s="22" t="n">
         <v>1.809</v>
       </c>
-      <c r="R25" s="52">
+      <c r="R25" s="23">
         <f>IFERROR(O25/P25,"")</f>
         <v/>
       </c>
-      <c r="S25" s="52">
+      <c r="S25" s="23">
         <f>IFERROR(AVERAGE(R23:R25),"")</f>
         <v/>
       </c>
-      <c r="T25" s="52">
+      <c r="T25" s="23">
         <f>IFERROR(SLOPE(Q21:Q25,ROW(Q21:Q25)),"")</f>
         <v/>
       </c>
-      <c r="U25" s="53">
+      <c r="U25" s="24">
         <f>IFERROR(O25/O22-1,"")</f>
         <v/>
       </c>
-      <c r="V25" s="53">
+      <c r="V25" s="24">
         <f>IFERROR(P25/P22-1,"")</f>
         <v/>
       </c>
-      <c r="AA25" s="50" t="n"/>
-      <c r="AJ25" s="47">
+      <c r="AA25" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>21594546</v>
+      </c>
+      <c r="AJ25" s="18">
         <f>IF(OR(AB25="",D25="",D25=0),"",AB25/D25)</f>
         <v/>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="29">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Gate=2.9112M | DEX_BSC(PancakeSwap)=18.6833M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B26" s="45" t="n">
+      <c r="B26" s="16" t="n">
         <v>0.0156768626998776</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="24">
         <f>IFERROR(B26/B25-1,"")</f>
         <v/>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="17" t="n">
         <v>16919045.11194</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="18" t="n">
         <v>0.4851199670476778</v>
       </c>
-      <c r="F26" s="48" t="n">
+      <c r="F26" s="19" t="n">
         <v>0.0003430716666666</v>
       </c>
-      <c r="G26" s="48" t="n">
+      <c r="G26" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H26" s="48" t="n">
+      <c r="H26" s="19" t="n">
         <v>0.00065669</v>
       </c>
-      <c r="I26" s="49" t="n">
+      <c r="I26" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L26" s="46" t="n">
+      <c r="L26" s="17" t="n">
         <v>6602997.42389184</v>
       </c>
-      <c r="M26" s="54" t="n">
+      <c r="M26" s="25" t="n">
         <v>1.6051</v>
       </c>
-      <c r="O26" s="51" t="n">
+      <c r="O26" s="22" t="n">
         <v>2.0591</v>
       </c>
-      <c r="P26" s="51" t="n">
+      <c r="P26" s="22" t="n">
         <v>1.3596</v>
       </c>
-      <c r="Q26" s="51" t="n">
+      <c r="Q26" s="22" t="n">
         <v>1.3691</v>
       </c>
-      <c r="R26" s="52">
+      <c r="R26" s="23">
         <f>IFERROR(O26/P26,"")</f>
         <v/>
       </c>
-      <c r="S26" s="52">
+      <c r="S26" s="23">
         <f>IFERROR(AVERAGE(R24:R26),"")</f>
         <v/>
       </c>
-      <c r="T26" s="52">
+      <c r="T26" s="23">
         <f>IFERROR(SLOPE(Q22:Q26,ROW(Q22:Q26)),"")</f>
         <v/>
       </c>
-      <c r="U26" s="53">
+      <c r="U26" s="24">
         <f>IFERROR(O26/O23-1,"")</f>
         <v/>
       </c>
-      <c r="V26" s="53">
+      <c r="V26" s="24">
         <f>IFERROR(P26/P23-1,"")</f>
         <v/>
       </c>
-      <c r="AA26" s="50" t="n"/>
-      <c r="AJ26" s="47">
+      <c r="AA26" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>12497899</v>
+      </c>
+      <c r="AJ26" s="18">
         <f>IF(OR(AB26="",D26="",D26=0),"",AB26/D26)</f>
         <v/>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="29">
-      <c r="A27" s="44" t="inlineStr">
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>IDOL: no Binance spot. Gate spot 28/07+ via one-shot probe (api.gateio.ws). taker_spot=ABSTAIN (L-29) | Gate=2.6639M | DEX_BSC(PancakeSwap)=9.8340M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B27" s="45" t="n">
+      <c r="B27" s="16" t="n">
         <v>0.0168086900086867</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="24">
         <f>IFERROR(B27/B26-1,"")</f>
         <v/>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="17" t="n">
         <v>5930775.03944</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="18" t="n">
         <v>0.4801954465121114</v>
       </c>
-      <c r="F27" s="48" t="n">
+      <c r="F27" s="19" t="n">
         <v>0.0001975616666666</v>
       </c>
-      <c r="G27" s="48" t="n">
+      <c r="G27" s="19" t="n">
         <v>5.655e-05</v>
       </c>
-      <c r="H27" s="48" t="n">
+      <c r="H27" s="19" t="n">
         <v>0.00035535</v>
       </c>
-      <c r="I27" s="49" t="n">
+      <c r="I27" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J27" s="28" t="n"/>
-      <c r="L27" s="46" t="n">
+      <c r="L27" s="17" t="n">
         <v>10710505.52576626</v>
       </c>
-      <c r="M27" s="54" t="n"/>
-      <c r="O27" s="51" t="n">
+      <c r="M27" s="25" t="n"/>
+      <c r="O27" s="22" t="n">
         <v>2.2065</v>
       </c>
-      <c r="P27" s="51" t="n">
+      <c r="P27" s="22" t="n">
         <v>0.992</v>
       </c>
-      <c r="Q27" s="51" t="n">
+      <c r="Q27" s="22" t="n">
         <v>1.0379</v>
       </c>
-      <c r="R27" s="52">
+      <c r="R27" s="23">
         <f>IFERROR(O27/P27,"")</f>
         <v/>
       </c>
-      <c r="S27" s="52">
+      <c r="S27" s="23">
         <f>IFERROR(AVERAGE(R25:R27),"")</f>
         <v/>
       </c>
-      <c r="T27" s="52">
+      <c r="T27" s="23">
         <f>IFERROR(Q27/Q22,"")</f>
         <v/>
       </c>
-      <c r="U27" s="53">
+      <c r="U27" s="24">
         <f>IFERROR(O27/O24-1,"")</f>
         <v/>
       </c>
-      <c r="V27" s="53">
+      <c r="V27" s="24">
         <f>IFERROR(P27/P24-1,"")</f>
         <v/>
       </c>
-      <c r="AA27" s="50" t="n"/>
-      <c r="AJ27" s="47">
+      <c r="AA27" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>2386498</v>
+      </c>
+      <c r="AJ27" s="18">
         <f>IF(OR(AB27="",D27="",D27=0),"",AB27/D27)</f>
         <v/>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="29">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Gate=0.6159M | DEX_BSC(PancakeSwap)=1.7706M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B28" s="45" t="n">
+      <c r="B28" s="16" t="n">
         <v>0.0156874869638988</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="24">
         <f>IFERROR(B28/B27-1,"")</f>
         <v/>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="17" t="n">
         <v>3001087.06951</v>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="18" t="n">
         <v>0.4725181981221648</v>
       </c>
-      <c r="F28" s="48" t="n">
+      <c r="F28" s="19" t="n">
         <v>6.6775e-05</v>
       </c>
-      <c r="G28" s="48" t="n">
+      <c r="G28" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H28" s="48" t="n">
+      <c r="H28" s="19" t="n">
         <v>0.00014646</v>
       </c>
-      <c r="I28" s="49" t="n">
+      <c r="I28" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J28" s="28" t="n"/>
-      <c r="K28" s="28" t="n"/>
-      <c r="L28" s="46" t="n">
+      <c r="L28" s="17" t="n">
         <v>9909666.0182763</v>
       </c>
-      <c r="M28" s="54" t="n"/>
-      <c r="O28" s="51" t="n">
+      <c r="M28" s="25" t="n"/>
+      <c r="O28" s="22" t="n">
         <v>2.3278</v>
       </c>
-      <c r="P28" s="51" t="n">
+      <c r="P28" s="22" t="n">
         <v>1.1608</v>
       </c>
-      <c r="Q28" s="51" t="n">
+      <c r="Q28" s="22" t="n">
         <v>1.3895</v>
       </c>
-      <c r="R28" s="52">
+      <c r="R28" s="23">
         <f>IFERROR(O28/P28,"")</f>
         <v/>
       </c>
-      <c r="S28" s="52">
+      <c r="S28" s="23">
         <f>IFERROR(AVERAGE(R26:R28),"")</f>
         <v/>
       </c>
-      <c r="T28" s="52">
+      <c r="T28" s="23">
         <f>IFERROR(Q28/Q23,"")</f>
         <v/>
       </c>
-      <c r="U28" s="53">
+      <c r="U28" s="24">
         <f>IFERROR(O28/O25-1,"")</f>
         <v/>
       </c>
-      <c r="V28" s="53">
+      <c r="V28" s="24">
         <f>IFERROR(P28/P25-1,"")</f>
         <v/>
       </c>
-      <c r="AA28" s="50" t="n"/>
-      <c r="AJ28" s="47">
+      <c r="AA28" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>1325917</v>
+      </c>
+      <c r="AJ28" s="18">
         <f>IF(OR(AB28="",D28="",D28=0),"",AB28/D28)</f>
         <v/>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="29">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Gate=0.1990M | DEX_BSC(PancakeSwap)=1.1269M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B29" s="45" t="n">
+      <c r="B29" s="16" t="n">
         <v>0.0152342446246339</v>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="24">
         <f>IFERROR(B29/B28-1,"")</f>
         <v/>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="17" t="n">
         <v>2995738.46077</v>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="18" t="n">
         <v>0.5284798189362505</v>
       </c>
-      <c r="F29" s="48" t="n">
+      <c r="F29" s="19" t="n">
         <v>9.596166666666668e-05</v>
       </c>
-      <c r="G29" s="48" t="n">
+      <c r="G29" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H29" s="48" t="n">
+      <c r="H29" s="19" t="n">
         <v>0.00020606</v>
       </c>
-      <c r="I29" s="49" t="n">
+      <c r="I29" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J29" s="28" t="n"/>
-      <c r="L29" s="46" t="n">
+      <c r="L29" s="17" t="n">
         <v>8867578.2372005</v>
       </c>
-      <c r="M29" s="54" t="n"/>
-      <c r="O29" s="51" t="n">
+      <c r="M29" s="25" t="n"/>
+      <c r="O29" s="22" t="n">
         <v>2.5585</v>
       </c>
-      <c r="P29" s="51" t="n">
+      <c r="P29" s="22" t="n">
         <v>1.209</v>
       </c>
-      <c r="Q29" s="51" t="n">
+      <c r="Q29" s="22" t="n">
         <v>1.4594</v>
       </c>
-      <c r="R29" s="52">
+      <c r="R29" s="23">
         <f>IFERROR(O29/P29,"")</f>
         <v/>
       </c>
-      <c r="S29" s="52">
+      <c r="S29" s="23">
         <f>IFERROR(AVERAGE(R27:R29),"")</f>
         <v/>
       </c>
-      <c r="T29" s="52">
+      <c r="T29" s="23">
         <f>IFERROR(Q29/Q24,"")</f>
         <v/>
       </c>
-      <c r="U29" s="53">
+      <c r="U29" s="24">
         <f>IFERROR(O29/O26-1,"")</f>
         <v/>
       </c>
-      <c r="V29" s="53">
+      <c r="V29" s="24">
         <f>IFERROR(P29/P26-1,"")</f>
         <v/>
       </c>
-      <c r="AA29" s="50" t="n"/>
-      <c r="AJ29" s="47">
+      <c r="AA29" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>1377252</v>
+      </c>
+      <c r="AJ29" s="18">
         <f>IF(OR(AB29="",D29="",D29=0),"",AB29/D29)</f>
         <v/>
       </c>
-      <c r="AL29" s="50" t="n"/>
-      <c r="AN29" s="50" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="29">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="AL29" s="21" t="n"/>
+      <c r="AN29" s="21" t="inlineStr">
+        <is>
+          <t>Gate=0.3526M | DEX_BSC(PancakeSwap)=1.0247M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n">
+      <c r="B30" s="16" t="n">
         <v>0.01640271991529722</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="24">
         <f>IFERROR(B30/B29-1,"")</f>
         <v/>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="17" t="n">
         <v>7335938.84066</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="18" t="n">
         <v>0.4987468671679198</v>
       </c>
-      <c r="F30" s="48" t="n">
+      <c r="F30" s="19" t="n">
         <v>0.00031801</v>
       </c>
-      <c r="G30" s="48" t="n">
+      <c r="G30" s="19" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H30" s="48" t="n">
+      <c r="H30" s="19" t="n">
         <v>0.00080377</v>
       </c>
-      <c r="I30" s="49" t="n">
+      <c r="I30" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="28" t="n"/>
-      <c r="L30" s="46" t="n">
+      <c r="L30" s="17" t="n">
         <v>8805698.412641199</v>
       </c>
-      <c r="M30" s="54" t="n"/>
-      <c r="O30" s="51" t="n">
+      <c r="M30" s="25" t="n"/>
+      <c r="O30" s="22" t="n">
         <v>2.5455</v>
       </c>
-      <c r="P30" s="51" t="n">
+      <c r="P30" s="22" t="n">
         <v>1.2396</v>
       </c>
-      <c r="Q30" s="51" t="n">
+      <c r="Q30" s="22" t="n">
         <v>1.5575</v>
       </c>
-      <c r="R30" s="52">
+      <c r="R30" s="23">
         <f>IFERROR(O30/P30,"")</f>
         <v/>
       </c>
-      <c r="S30" s="52">
+      <c r="S30" s="23">
         <f>IFERROR(AVERAGE(R28:R30),"")</f>
         <v/>
       </c>
-      <c r="T30" s="52">
+      <c r="T30" s="23">
         <f>IFERROR(Q30/Q25,"")</f>
         <v/>
       </c>
-      <c r="U30" s="53">
+      <c r="U30" s="24">
         <f>IFERROR(O30/O27-1,"")</f>
         <v/>
       </c>
-      <c r="V30" s="53">
+      <c r="V30" s="24">
         <f>IFERROR(P30/P27-1,"")</f>
         <v/>
       </c>
-      <c r="W30" s="50" t="n"/>
-      <c r="AA30" s="50" t="n"/>
-      <c r="AB30" s="46" t="n"/>
-      <c r="AC30" s="28" t="n"/>
-      <c r="AD30" s="46" t="n"/>
-      <c r="AE30" s="46" t="n"/>
-      <c r="AJ30" s="47">
+      <c r="W30" s="21" t="n"/>
+      <c r="AA30" s="21" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB30" s="17" t="n">
+        <v>1544874</v>
+      </c>
+      <c r="AD30" s="17" t="n"/>
+      <c r="AE30" s="17" t="n"/>
+      <c r="AJ30" s="18">
         <f>IF(OR(AB30="",D30="",D30=0),"",AB30/D30)</f>
         <v/>
       </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>Gate=0.1104M | DEX_BSC(PancakeSwap)=1.4345M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B31" t="n">
         <v>0.0239455254881411</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31">
         <f>IFERROR(B31/B30-1,"")</f>
         <v/>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" t="n">
         <v>175671534.50156</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E31" t="n">
         <v>0.5152925209635985</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" t="n">
         <v>9.492333333333332e-05</v>
       </c>
-      <c r="G31" s="28" t="n">
+      <c r="G31" t="n">
         <v>-0.00070055</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" t="n">
         <v>0.00066625</v>
       </c>
-      <c r="I31" s="28" t="n">
+      <c r="I31" t="n">
         <v>6</v>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="L31" s="28" t="n">
+      <c r="L31" t="n">
         <v>9844799.294609999</v>
       </c>
-      <c r="M31" s="28" t="n">
+      <c r="M31" t="n">
         <v>1.4493</v>
       </c>
-      <c r="N31" s="28" t="n"/>
-      <c r="O31" s="28" t="n">
+      <c r="O31" t="n">
         <v>2.5241</v>
       </c>
-      <c r="P31" s="28" t="n">
+      <c r="P31" t="n">
         <v>1.1825</v>
       </c>
-      <c r="Q31" s="28" t="n">
+      <c r="Q31" t="n">
         <v>1.4888</v>
       </c>
-      <c r="R31" s="28">
+      <c r="R31">
         <f>IFERROR(O31/P31,"")</f>
         <v/>
       </c>
-      <c r="S31" s="28">
+      <c r="S31">
         <f>IFERROR(AVERAGE(R29:R31),"")</f>
         <v/>
       </c>
-      <c r="T31" s="28">
+      <c r="T31">
         <f>IFERROR(SLOPE(Q27:Q31,ROW(Q27:Q31)),"")</f>
         <v/>
       </c>
-      <c r="U31" s="28">
+      <c r="U31">
         <f>IFERROR(O31/O28-1,"")</f>
         <v/>
       </c>
-      <c r="V31" s="28">
+      <c r="V31">
         <f>IFERROR(P31/P28-1,"")</f>
         <v/>
       </c>
-      <c r="Z31" s="28" t="n"/>
-      <c r="AA31" s="28" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="AB31" s="28" t="n">
-        <v>9577588</v>
-      </c>
-      <c r="AC31" s="28" t="n"/>
-      <c r="AJ31" s="28">
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>41408688</v>
+      </c>
+      <c r="AC31" t="n"/>
+      <c r="AJ31">
         <f>IF(OR(AB31="",D31="",D31=0),"",AB31/D31)</f>
         <v/>
       </c>
-      <c r="AN31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="29">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>Gate=9.5776M | DEX_BSC(PancakeSwap)=31.8311M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" t="n">
         <v>0.02311694285969805</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32">
         <f>IFERROR(B32/B31-1,"")</f>
         <v/>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" t="n">
         <v>40715280.86713</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" t="n">
         <v>0.500848557452331</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" t="n">
         <v>5e-05</v>
       </c>
-      <c r="G32" s="28" t="n">
+      <c r="G32" t="n">
         <v>5e-05</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" t="n">
         <v>5e-05</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" t="n">
         <v>6</v>
       </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K32" s="28" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="28" t="n">
+      <c r="L32" t="n">
         <v>10483341.9772</v>
       </c>
-      <c r="M32" s="28" t="n">
+      <c r="M32" t="n">
         <v>1.4806</v>
       </c>
-      <c r="O32" s="28" t="n">
+      <c r="O32" t="n">
         <v>1.7314</v>
       </c>
-      <c r="P32" s="28" t="n">
+      <c r="P32" t="n">
         <v>1.1782</v>
       </c>
-      <c r="Q32" s="28" t="n">
+      <c r="Q32" t="n">
         <v>1.1436</v>
       </c>
-      <c r="R32" s="28">
+      <c r="R32">
         <f>IFERROR(O32/P32,"")</f>
         <v/>
       </c>
-      <c r="S32" s="28">
+      <c r="S32">
         <f>IFERROR(AVERAGE(R30:R32),"")</f>
         <v/>
       </c>
-      <c r="T32" s="28">
+      <c r="T32">
         <f>IFERROR(SLOPE(Q28:Q32,ROW(Q28:Q32)),"")</f>
         <v/>
       </c>
-      <c r="U32" s="28">
+      <c r="U32">
         <f>IFERROR(O32/O29-1,"")</f>
         <v/>
       </c>
-      <c r="V32" s="28">
+      <c r="V32">
         <f>IFERROR(P32/P29-1,"")</f>
         <v/>
       </c>
-      <c r="AA32" s="28" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="AB32" s="28" t="n">
-        <v>1547487</v>
-      </c>
-      <c r="AC32" s="28" t="n"/>
-      <c r="AJ32" s="28">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Gate+dex_bsc</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>8866587</v>
+      </c>
+      <c r="AC32" t="n"/>
+      <c r="AJ32">
         <f>IF(OR(AB32="",D32="",D32=0),"",AB32/D32)</f>
         <v/>
       </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>Gate=1.5475M | DEX_BSC(PancakeSwap)=7.3191M | src=GeckoTerminal one-shot 2026-08-03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11" customWidth="1" style="28" min="1" max="1"/>
-    <col width="60" customWidth="1" style="28" min="2" max="2"/>
-    <col width="18" customWidth="1" style="28" min="3" max="3"/>
-    <col width="45" customWidth="1" style="28" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>D. NHAT KY DIEN BIEN (append-only, moi nhat duoi cung)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="55" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>ngay</t>
         </is>
       </c>
-      <c r="B3" s="55" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>su_kien_so_lieu</t>
         </is>
       </c>
-      <c r="C3" s="55" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>nguon</t>
         </is>
       </c>
-      <c r="D3" s="55" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>doc_nhanh</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="33" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>31/07→02/08</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>13 vi nhan ~273M IDOL (~5.7% supply) tu Binance. 7 vi x20M chia may (Sent=0, hold). 58bro nhan 51.36M, sent 27.06M (trung chuyen — dich PENDING). Ngay chinh xac PENDING. PUMP_STAGING?/RELOCATION? — CHUA GAN, can infra_gate label-check truoc (&gt;=2% supply, an TAG/Bitget)</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Binance (Alpha custody) — cơ chế xác nhận 03/08</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PENDING-VERIFY: txhash + ngay chinh xac tu Nansen. Doc: rut TRONG markup (gia len 0.016→0.024 01-02/08) — hai khuon canh tranh: (1) that float leg-2 (ESPORTS-10% pattern) vs (2) chot chien loi pham on-chain. E1 han cap -&gt; P3: can operator feed dia chi + txhash de phan loai. | [Z4-rev 03/08] GOM-qua-Alpha = giả thuyết dẫn đầu về cơ chế: 273M IDOL rút về ví BSC (0x...) có thể là GOM staging qua Binance Alpha custody. Mechanism: Binance giữ IDOL on-chain → users mua qua Binance app (Alpha section) → Binance rút batch về ví custody BSC → 7×~39M = 273M. Xác nhận còn thiếu (Z1): txhash + địa chỉ đích 13 ví. Nếu Z1 confirm Binance custody → E1 = GOM-staging, không phải chốt lợi nhuận. Nếu Z1 thấy pattern khác → revise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gate wallet 0x0d0707 +54.76M IDOL (~1.14% supply) trong 1d; +148.29M trong 30d. Huong: DEPOSIT vao Gate. Y dinh: PENDING — can ma tran BTW-vs-IDOL + vi tri chu ky tu B5</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Nansen UI (so hua, chua co txhash)</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
-        <is>
-          <t>PENDING-VERIFY: txhash + ngay chinh xac tu Nansen. Doc: rut TRONG markup (gia len 0.016→0.024 01-02/08) — hai khuon canh tranh: (1) that float leg-2 (ESPORTS-10% pattern) vs (2) chot chien loi pham on-chain. E1 han cap -&gt; P3: can operator feed dia chi + txhash de phan loai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>Gate wallet 0x0d0707 +54.76M IDOL (~1.14% supply) trong 1d; +148.29M trong 30d. Huong: DEPOSIT vao Gate. Y dinh: PENDING — can ma tran BTW-vs-IDOL + vi tri chu ky tu B5</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>Nansen UI (so hua, chua co txhash)</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>[HA CAP] &lt;2% supply — khong dang ke tren on-chain thesis. Giu dong lam vet. PENDING-VERIFY: txhash + phan loai BTW-vs-IDOL (Gate wallet 0x0d0707 co phai cung operator BTW khong?)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unlock tranche tháng 8: 97.29M IDOL (~2.03% supply)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UNLOCK_SCHEDULE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Suppressor context thường trực: 2%/tháng ngày 11. Markup 01/08 nổ 10 ngày TRƯỚC — unlock ≠ trigger E1 (W6: UNLIKELY). Nguồn: CoinLaunch (op-verified). Team/Strat/Priv vừa ra linear post-cliff 06/2026.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="22" customWidth="1" style="28" min="2" max="2"/>
-    <col width="44" customWidth="1" style="28" min="3" max="3"/>
-    <col width="40" customWidth="1" style="28" min="4" max="4"/>
-    <col width="22" customWidth="1" style="28" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>C. CHOT THEO DOI — doc moi ngay sau nen dong</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="55" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="55" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>chot</t>
         </is>
       </c>
-      <c r="C3" s="55" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>dieu_kien</t>
         </is>
       </c>
-      <c r="D3" s="55" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>nghia_khi_bat</t>
         </is>
       </c>
-      <c r="E3" s="55" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>trang_thai_hom_nay</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="33" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Redeposit bat ky vi nao trong cum 13</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Bat ky vi trong cum 13 ~273M gui lai len san (BscScan detect)</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>DONG AN XA TUC THOI — tiet lo y dinh muon ban; khong gia han wait</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>CHUA BAT — watcher 0-credit pending B5</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="33" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>gLSR flush &lt;=1.1 + funding tai ghin &gt;=3d</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>glsr &lt;= 1.1 lien tuc &gt;=3 nen VA f_avg &lt;= 5e-5 &gt;=3 nen</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Ho so re-staging leg-2 song — theo doi luc luong crowd short nap nhien lieu</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>THEO DOI — 02/08 glsr=1.1436 (can them 03/08 de confirm trend)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="33" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>pos_r floor hau-sap</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>pos_r &gt;= 1.6 tai OI floor = con ghe (dinh luat #9); ga &lt; 1.3 = ghe rong</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Con ghe -&gt; re-staging kha thi; Ghe rong -&gt; dong an/tra gia gap</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>THEO DOI — 02/08 pos_r=1.731 (&gt; 1.6, con ghe); OI=10.48M; cho 03/08</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="33" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Suppressor bat ky (L-27 §5)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>dist_wall &lt; L-27_thresh HOAC neg_div ben &gt;= 3d HOAC post_climax flag</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>STAND_ASIDE — khong vao/them bat ke phe nao</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CHO SO — cols 23/24 chua co gia tri (formula chua tinh)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="7" customWidth="1" style="28" min="1" max="1"/>
-    <col width="11" customWidth="1" style="28" min="2" max="2"/>
-    <col width="12" customWidth="1" style="28" min="3" max="3"/>
-    <col width="9" customWidth="1" style="28" min="4" max="4"/>
-    <col width="16" customWidth="1" style="28" min="5" max="5"/>
-    <col width="13" customWidth="1" style="28" min="6" max="6"/>
-    <col width="9" customWidth="1" style="28" min="7" max="7"/>
-    <col width="42" customWidth="1" style="28" min="8" max="9"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>E. OUTCOME — dien tai moc; verdict_check: verdict luc mo DUNG/SAI o diem nao</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="55" t="n"/>
-      <c r="B3" s="55" t="n"/>
-      <c r="C3" s="55" t="n"/>
-      <c r="D3" s="55" t="n"/>
-      <c r="E3" s="55" t="n"/>
-      <c r="F3" s="55" t="n"/>
-      <c r="G3" s="55" t="n"/>
-      <c r="H3" s="55" t="n"/>
-      <c r="I3" s="55" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="33" t="n"/>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="34" t="n"/>
-      <c r="D4" s="34" t="n"/>
-      <c r="E4" s="34" t="n"/>
-      <c r="F4" s="34" t="n"/>
-      <c r="G4" s="34" t="n"/>
-      <c r="H4" s="34" t="n"/>
-      <c r="I4" s="34" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="33" t="n"/>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="34" t="n"/>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="34" t="n"/>
-      <c r="H5" s="34" t="n"/>
-      <c r="I5" s="34" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n"/>
-      <c r="F7" s="34" t="n"/>
-      <c r="G7" s="34" t="n"/>
-      <c r="H7" s="34" t="n"/>
-      <c r="I7" s="34" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="26" t="n"/>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="95" customWidth="1" style="28" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>I. MM / OPERATOR PROFILE — van tay hanh vi (moi MM danh mot kieu)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>MM cong bo / nghi van</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>unknown — chua co ho so listing chinh thuc; can tra (PENDING)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="32" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>MM_ID</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>unknown-IDOL (chua du 3 van tay de gan; nghi khuon AKE/bid-walk theo hanh vi staging that)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="32" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Van tay funding</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Sau markup 01/08 (+50% 1 nen), f_avg 02/08 = 5e-5 (san/pinned). Trong nghia: MM chu dong de gim funding ve san sau markup — crowd khong chase (khong co premium demand); CONSISTENT EVAA khuon (re-staging, khong phai climax). Taker 01/08 = 51.5% (&lt;55%) = bid-walk, khong drive up funding. VAN TAY: pin-post-markup + taker&lt;55% = BIDWALK-A fingerprint.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="32" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Van tay markup</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>01/08: vol_q=175.67M (~10x nen binh quan 28-31/07 ~17M), taker=51.5% (duoi 55% suot ca cu markup) — bid-walk ro rang. OI: 27/07 6.60M → 28/07 10.71M (+62%) → 01/08 9.84M → 02/08 10.48M. pos_r: leo 2.059→2.558 truoc ignition, sap 2.524→1.731 sau markup. Timing: top longs loaded 28-31/07 (pre-ignition), exit 02/08 khi crowd gap vao (OI tang nhung pos_r sap). KHUON NGHI VAN: BIDWALK-A (bid limit trong khi taker bearish/neutral).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="32" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ky thuat quan crowd</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>23/07 vol spike (167M, 8x nen) - bait-probe NGHI VAN (can taker 23/07). 28/07 OI +62% nhung taker=0.480 (bear) = MM mua limit trong khi retail sell. 01/08 markup: taker 51.5% — crowd KHONG phat hien hoac khong dan vao, MM lam gia don gian. 31/07→02/08 rut on-chain 273M TRONG markup = phuc tap: hoac thang float (giam supply san), hoac chot loi on-chain. gLSR: 1.369→1.038 (28/07, crowd giam short) → leo 1.558 (31/07) → sap 1.144 (02/08, crowd tiep tuc unwind).</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="A8" s="32" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ky thuat moi on-chain</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>staging that (7 vi x20M hold, Sent=0) — GIONG BANK; nghi MM-BIDWALK-A khuon</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="A9" s="32" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Binance perp (chinh, OI uu the); Gate spot (bai do / deposit point)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="A10" s="32" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cross-campaign</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>PENDING — ma tran BTW-vs-IDOL: Gate wallet 0x0d0707 co lien he BTW khong? E2 ha cap (&lt;2% supply) nhung van giu vet de check cross-campaign. Can: operator feed txhash va label cho 0x0d0707.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Ung xu voi minh</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>MM_ID: unknown-IDOL (nghi BIDWALK-A khuon). Du kien 3 van tay can xac nhan: (1) BIDWALK-A: markup taker&lt;55% DONE (01/08 = 51.5%); (2) Bait-probe: vol spike 23/07, PENDING taker; (3) On-chain staging: 7 vi x20M Sent=0 — DONE (giong BANK). Neu bait-probe confirm: so sanh voi AKE/BANK MM_BOOK. Verdict MM_ID: TAM THOI BIDWALK-A, cho them du lieu.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n"/>
+      <c r="A12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n"/>
+      <c r="A13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n"/>
+      <c r="A14" t="n"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="95" customWidth="1" style="28" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="29">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="16.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>J. TOKENOMICS / UNLOCK — dong cung co lich, MM danh quanh no</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Circulating / Total (uoc tinh)</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
-        <is>
-          <t>~4.79B IDOL (uoc tinh tu E1: 273M=5.7% supply); chinh xac PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>4,800,000,000 IDOL total supply (CoinLaunch). Circulating ≈ 32.49% × 4.8B = 1,559.5M. E1 basis: 273M = 5.7% total supply ✓ (khớp ~4.79B estimate cũ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Nguon tra</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
-        <is>
-          <t>Tokenomist, CryptoRank, project docs — da thu khong co ket qua (NO_DATA 2026-08-03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>CoinLaunch (operator-verified 2026-08-03). Đã thử: Tokenomist → NO_DATA, CryptoRank → NO_DATA (lần 1+2). CoinLaunch: có đủ schedule theo từng category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Unlock KE TIEP</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>NO_DATA — khong tim thay lich unlock tu nguon free</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11 (T+8): 97,290,000 IDOL (~2.03% supply). Breakdown: Community 35.46M / Eco 17.63M / Team 28.8M / Strategic 7.68M / Private 5.76M / Advisor 1.96M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Unlock 90 ngay toi</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>NO_DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3 tranches: 11/08 + 11/09 + 11/10 = 97.29M × 3 = 291.87M (~6.08% supply). Team/Strat/Private: đang linear (cliff hết 06/2026, 2 tranche còn tính từ 07/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Cliff da qua gan nhat</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>NO_DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Team (cliff hết 06/2026), Strategic (cliff hết 06/2026), Private (cliff hết 06/2026). Cả 3 category vừa ra linear period → tháng 8 là lần đầu Team/Strat/Priv unlock post-cliff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Doc</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>L-12: can unlock de biet moc deadline MM (keo truoc/de truoc unlock). Operator: tra Tokenomist.io + CryptoRank + docs du an. Neu co unlock lon 30-60d toi -&gt; kich ban keo-truoc-unlock vao EVENTS.</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>L-12: cần unlock để biết mốc deadline MM. W6: UNLOCK-VESTING = UNLIKELY (3 trượt — xem row 14). Suppressor: unlock 2%/tháng = áp lực cung thường trực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TGE_date</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>unlocked_pct</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>32.49% (tính đến 2026-08-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>monthly_unlock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>97,290,000 IDOL ngày 11 hằng tháng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W6_unlock_verdict</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UNLIKELY — 3 trượt cứng: (1) Ngày ✗: E1 rút 31/07→02/08 vs vesting ngày 11th (10 ngày trước); (2) Cỡ ✗: 273M rút ≠ 97.29M tranche (gấp 2.8×); (3) Nguồn ✗: rút từ ví exchange ≠ disburse từ vesting contract trực tiếp. 7×20M = chia-máy-khi-rút (TAG-5-ví khuôn), không phải vesting tranche pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hypothesis_remaining</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Còn 2 giả thuyết: (A) STAGING-thắt-float: rút để giảm cung sàn, chuẩn bị leg-2 markup; (B) CHỐT-LỢI-PHẨM: chuẩn bị bank lợi nhuận sau markup 01/08. Phân biệt: A → không redeposit + OI giữ; B → redeposit sau 2-4w hoặc dump perp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>suppressor_context</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Markup 01/08 nổ 10 ngày TRƯỚC tranche 11/08. Unlock 2%/tháng = áp lực cung THƯỜNG TRỰC — không phải trigger đặc biệt của E1. T1 (watcher 13 ví) là trigger quan trọng hơn để phân loại A vs B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gate_spot_W3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gate.io spot (api.gateio.ws, one-shot probe 2026-08-03 01:49 UTC): 28/07=615,898 USDT / 29/07=199,017 / 30/07=352,552 / 31/07=110,374 / 01/08=9,577,588 / 02/08=1,547,487 USDT. Nguồn: scripts/archive/_probe_idol_gate_tape.py (public API, không cần key). W3 REVISION: không còn ABSTAIN — có Gate spot series đủ 28/07→02/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W2_gate_capacity</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>01/08 Gate spot vol = 9.58M USDT. 273M IDOL @ close 0.02438 = notional 6.66M USDT. Notional/vol = 69.5% → THIN (&lt; 2× absorption). Kết luận: Gate không đủ sức chứa 273M rút trong 1 ngày trên spot.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/docs/case_files/CASE_IDOL.xlsx
+++ b/docs/case_files/CASE_IDOL.xlsx
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AQ32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -992,6 +992,16 @@
           <t>mm_note</t>
         </is>
       </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>vol_alpha_usd</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>n_trades_alpha</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -1060,14 +1070,19 @@
       <c r="AB3" t="n">
         <v>223517</v>
       </c>
-      <c r="AJ3" s="18">
-        <f>IF(OR(AB3="",D3="",D3=0),"",AB3/D3)</f>
-        <v/>
+      <c r="AJ3" s="18" t="n">
+        <v>89644</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Gate=0.2235M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.2235M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.090M n=1,093</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>89644</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -1144,14 +1159,19 @@
       <c r="AB4" t="n">
         <v>261083</v>
       </c>
-      <c r="AJ4" s="18">
-        <f>IF(OR(AB4="",D4="",D4=0),"",AB4/D4)</f>
-        <v/>
+      <c r="AJ4" s="18" t="n">
+        <v>74307</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Gate=0.2611M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.2611M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.074M n=1,019</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>74307</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1019</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -1225,14 +1245,19 @@
       <c r="AB5" t="n">
         <v>1320492</v>
       </c>
-      <c r="AJ5" s="18">
-        <f>IF(OR(AB5="",D5="",D5=0),"",AB5/D5)</f>
-        <v/>
+      <c r="AJ5" s="18" t="n">
+        <v>256301</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Gate=1.3205M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=1.3205M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.256M n=2,191</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>256301</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2191</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1314,14 +1339,19 @@
       <c r="AB6" t="n">
         <v>1222066</v>
       </c>
-      <c r="AJ6" s="18">
-        <f>IF(OR(AB6="",D6="",D6=0),"",AB6/D6)</f>
-        <v/>
+      <c r="AJ6" s="18" t="n">
+        <v>2064500</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Gate=1.2221M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=1.2221M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$2.065M n=5,385</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>2064500</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5385</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -1403,14 +1433,19 @@
       <c r="AB7" t="n">
         <v>220426</v>
       </c>
-      <c r="AJ7" s="18">
-        <f>IF(OR(AB7="",D7="",D7=0),"",AB7/D7)</f>
-        <v/>
+      <c r="AJ7" s="18" t="n">
+        <v>3410181</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Gate=0.2204M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.2204M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$3.410M n=7,249</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>3410181</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7249</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -1495,14 +1530,19 @@
       <c r="AB8" t="n">
         <v>379886</v>
       </c>
-      <c r="AJ8" s="18">
-        <f>IF(OR(AB8="",D8="",D8=0),"",AB8/D8)</f>
-        <v/>
+      <c r="AJ8" s="18" t="n">
+        <v>143695</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Gate=0.3799M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.3799M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.144M n=1,414</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>143695</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1414</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1584,14 +1624,19 @@
       <c r="AB9" t="n">
         <v>116210</v>
       </c>
-      <c r="AJ9" s="18">
-        <f>IF(OR(AB9="",D9="",D9=0),"",AB9/D9)</f>
-        <v/>
+      <c r="AJ9" s="18" t="n">
+        <v>15239</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Gate=0.1162M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1162M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.015M n=201</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>15239</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>201</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1673,14 +1718,19 @@
       <c r="AB10" t="n">
         <v>121348</v>
       </c>
-      <c r="AJ10" s="18">
-        <f>IF(OR(AB10="",D10="",D10=0),"",AB10/D10)</f>
-        <v/>
+      <c r="AJ10" s="18" t="n">
+        <v>2083</v>
       </c>
       <c r="AN10" s="21" t="inlineStr">
         <is>
-          <t>Gate=0.1213M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1213M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.002M n=45</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>2083</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1766,14 +1816,19 @@
       <c r="AB11" t="n">
         <v>85543</v>
       </c>
-      <c r="AJ11" s="18">
-        <f>IF(OR(AB11="",D11="",D11=0),"",AB11/D11)</f>
-        <v/>
+      <c r="AJ11" s="18" t="n">
+        <v>10180</v>
       </c>
       <c r="AN11" s="21" t="inlineStr">
         <is>
-          <t>Gate=0.0855M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0855M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.010M n=150</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>10180</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1856,14 +1911,19 @@
       <c r="AB12" t="n">
         <v>137097</v>
       </c>
-      <c r="AJ12" s="18">
-        <f>IF(OR(AB12="",D12="",D12=0),"",AB12/D12)</f>
-        <v/>
+      <c r="AJ12" s="18" t="n">
+        <v>17739</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Gate=0.1371M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1371M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.018M n=225</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>17739</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>225</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1946,14 +2006,19 @@
       <c r="AB13" t="n">
         <v>356547</v>
       </c>
-      <c r="AJ13" s="18">
-        <f>IF(OR(AB13="",D13="",D13=0),"",AB13/D13)</f>
-        <v/>
+      <c r="AJ13" s="18" t="n">
+        <v>38235</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Gate=0.3565M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.3565M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.038M n=509</t>
+        </is>
+      </c>
+      <c r="AP13" t="n">
+        <v>38235</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>509</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -2036,14 +2101,19 @@
       <c r="AB14" t="n">
         <v>123180</v>
       </c>
-      <c r="AJ14" s="18">
-        <f>IF(OR(AB14="",D14="",D14=0),"",AB14/D14)</f>
-        <v/>
+      <c r="AJ14" s="18" t="n">
+        <v>48308</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Gate=0.1232M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1232M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.048M n=703</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>48308</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>703</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -2126,15 +2196,20 @@
       <c r="AB15" t="n">
         <v>333231</v>
       </c>
-      <c r="AJ15" s="18">
-        <f>IF(OR(AB15="",D15="",D15=0),"",AB15/D15)</f>
-        <v/>
+      <c r="AJ15" s="18" t="n">
+        <v>25205</v>
       </c>
       <c r="AL15" s="21" t="n"/>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Gate=0.3332M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.3332M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.025M n=378</t>
+        </is>
+      </c>
+      <c r="AP15" t="n">
+        <v>25205</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>378</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -2220,14 +2295,19 @@
       <c r="AB16" t="n">
         <v>78360</v>
       </c>
-      <c r="AJ16" s="18">
-        <f>IF(OR(AB16="",D16="",D16=0),"",AB16/D16)</f>
-        <v/>
+      <c r="AJ16" s="18" t="n">
+        <v>11109</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Gate=0.0784M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0784M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.011M n=152</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>11109</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -2310,14 +2390,19 @@
       <c r="AB17" t="n">
         <v>88198</v>
       </c>
-      <c r="AJ17" s="18">
-        <f>IF(OR(AB17="",D17="",D17=0),"",AB17/D17)</f>
-        <v/>
+      <c r="AJ17" s="18" t="n">
+        <v>14836</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Gate=0.0882M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0882M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.015M n=199</t>
+        </is>
+      </c>
+      <c r="AP17" t="n">
+        <v>14836</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -2400,14 +2485,19 @@
       <c r="AB18" t="n">
         <v>91266</v>
       </c>
-      <c r="AJ18" s="18">
-        <f>IF(OR(AB18="",D18="",D18=0),"",AB18/D18)</f>
-        <v/>
+      <c r="AJ18" s="18" t="n">
+        <v>1236751</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Gate=0.0913M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0913M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$1.237M n=668</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>1236751</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>668</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -2490,14 +2580,19 @@
       <c r="AB19" t="n">
         <v>119616</v>
       </c>
-      <c r="AJ19" s="18">
-        <f>IF(OR(AB19="",D19="",D19=0),"",AB19/D19)</f>
-        <v/>
+      <c r="AJ19" s="18" t="n">
+        <v>69050</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Gate=0.1196M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1196M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.069M n=770</t>
+        </is>
+      </c>
+      <c r="AP19" t="n">
+        <v>69050</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -2579,14 +2674,19 @@
       <c r="AB20" t="n">
         <v>75888</v>
       </c>
-      <c r="AJ20" s="18">
-        <f>IF(OR(AB20="",D20="",D20=0),"",AB20/D20)</f>
-        <v/>
+      <c r="AJ20" s="18" t="n">
+        <v>67415</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Gate=0.0759M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0759M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.067M n=575</t>
+        </is>
+      </c>
+      <c r="AP20" t="n">
+        <v>67415</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>575</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2668,14 +2768,19 @@
       <c r="AB21" t="n">
         <v>77524</v>
       </c>
-      <c r="AJ21" s="18">
-        <f>IF(OR(AB21="",D21="",D21=0),"",AB21/D21)</f>
-        <v/>
+      <c r="AJ21" s="18" t="n">
+        <v>22634</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Gate=0.0775M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0775M | DEX_BSC(PancakeSwap)=N/A | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.023M n=228</t>
+        </is>
+      </c>
+      <c r="AP21" t="n">
+        <v>22634</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>228</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2757,14 +2862,19 @@
       <c r="AB22" t="n">
         <v>1687010</v>
       </c>
-      <c r="AJ22" s="18">
-        <f>IF(OR(AB22="",D22="",D22=0),"",AB22/D22)</f>
-        <v/>
+      <c r="AJ22" s="18" t="n">
+        <v>0.0423</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Gate=0.1552M | DEX_BSC(PancakeSwap)=1.5318M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1552M | DEX_BSC(PancakeSwap)=1.5318M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.065M n=567 suspect=0.042x</t>
+        </is>
+      </c>
+      <c r="AP22" t="n">
+        <v>64824</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>567</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -2849,14 +2959,19 @@
       <c r="AB23" t="n">
         <v>657484</v>
       </c>
-      <c r="AJ23" s="18">
-        <f>IF(OR(AB23="",D23="",D23=0),"",AB23/D23)</f>
-        <v/>
+      <c r="AJ23" s="18" t="n">
+        <v>0.0468</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Gate=0.0942M | DEX_BSC(PancakeSwap)=0.5633M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0942M | DEX_BSC(PancakeSwap)=0.5633M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.026M n=261 suspect=0.047x</t>
+        </is>
+      </c>
+      <c r="AP23" t="n">
+        <v>26360</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2938,14 +3053,19 @@
       <c r="AB24" t="n">
         <v>482966</v>
       </c>
-      <c r="AJ24" s="18">
-        <f>IF(OR(AB24="",D24="",D24=0),"",AB24/D24)</f>
-        <v/>
+      <c r="AJ24" s="18" t="n">
+        <v>0.0278</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Gate=0.0287M | DEX_BSC(PancakeSwap)=0.4543M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.0287M | DEX_BSC(PancakeSwap)=0.4543M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.013M n=141 suspect=0.028x</t>
+        </is>
+      </c>
+      <c r="AP24" t="n">
+        <v>12611</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -3027,14 +3147,19 @@
       <c r="AB25" t="n">
         <v>21594546</v>
       </c>
-      <c r="AJ25" s="18">
-        <f>IF(OR(AB25="",D25="",D25=0),"",AB25/D25)</f>
-        <v/>
+      <c r="AJ25" s="18" t="n">
+        <v>0.2029</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Gate=2.9112M | DEX_BSC(PancakeSwap)=18.6833M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=2.9112M | DEX_BSC(PancakeSwap)=18.6833M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$3.792M n=27,245 suspect=0.203x</t>
+        </is>
+      </c>
+      <c r="AP25" t="n">
+        <v>3791767</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>27245</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -3116,14 +3241,19 @@
       <c r="AB26" t="n">
         <v>12497899</v>
       </c>
-      <c r="AJ26" s="18">
-        <f>IF(OR(AB26="",D26="",D26=0),"",AB26/D26)</f>
-        <v/>
+      <c r="AJ26" s="18" t="n">
+        <v>0.2928</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>IDOL: no Binance spot. Gate spot 28/07+ via one-shot probe (api.gateio.ws). taker_spot=ABSTAIN (L-29) | Gate=2.6639M | DEX_BSC(PancakeSwap)=9.8340M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>IDOL: no Binance spot. Gate spot 28/07+ via one-shot probe (api.gateio.ws). taker_spot=ABSTAIN (L-29) | Gate=2.6639M | DEX_BSC(PancakeSwap)=9.8340M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$2.880M n=14,835 suspect=0.293x</t>
+        </is>
+      </c>
+      <c r="AP26" t="n">
+        <v>2879862</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14835</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -3198,14 +3328,19 @@
       <c r="AB27" t="n">
         <v>2386498</v>
       </c>
-      <c r="AJ27" s="18">
-        <f>IF(OR(AB27="",D27="",D27=0),"",AB27/D27)</f>
-        <v/>
+      <c r="AJ27" s="18" t="n">
+        <v>0.0774</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Gate=0.6159M | DEX_BSC(PancakeSwap)=1.7706M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.6159M | DEX_BSC(PancakeSwap)=1.7706M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.137M n=1,463 suspect=0.077x</t>
+        </is>
+      </c>
+      <c r="AP27" t="n">
+        <v>137098</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1463</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -3280,14 +3415,19 @@
       <c r="AB28" t="n">
         <v>1325917</v>
       </c>
-      <c r="AJ28" s="18">
-        <f>IF(OR(AB28="",D28="",D28=0),"",AB28/D28)</f>
-        <v/>
+      <c r="AJ28" s="18" t="n">
+        <v>0.0994</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Gate=0.1990M | DEX_BSC(PancakeSwap)=1.1269M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1990M | DEX_BSC(PancakeSwap)=1.1269M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.112M n=1,169 suspect=0.099x</t>
+        </is>
+      </c>
+      <c r="AP28" t="n">
+        <v>112067</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1169</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -3362,15 +3502,20 @@
       <c r="AB29" t="n">
         <v>1377252</v>
       </c>
-      <c r="AJ29" s="18">
-        <f>IF(OR(AB29="",D29="",D29=0),"",AB29/D29)</f>
-        <v/>
+      <c r="AJ29" s="18" t="n">
+        <v>0.0784</v>
       </c>
       <c r="AL29" s="21" t="n"/>
       <c r="AN29" s="21" t="inlineStr">
         <is>
-          <t>Gate=0.3526M | DEX_BSC(PancakeSwap)=1.0247M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.3526M | DEX_BSC(PancakeSwap)=1.0247M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.080M n=775 suspect=0.078x</t>
+        </is>
+      </c>
+      <c r="AP29" t="n">
+        <v>80310</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -3448,14 +3593,19 @@
       </c>
       <c r="AD30" s="17" t="n"/>
       <c r="AE30" s="17" t="n"/>
-      <c r="AJ30" s="18">
-        <f>IF(OR(AB30="",D30="",D30=0),"",AB30/D30)</f>
-        <v/>
+      <c r="AJ30" s="18" t="n">
+        <v>0.1226</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Gate=0.1104M | DEX_BSC(PancakeSwap)=1.4345M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=0.1104M | DEX_BSC(PancakeSwap)=1.4345M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.176M n=1,398 suspect=0.123x</t>
+        </is>
+      </c>
+      <c r="AP30" t="n">
+        <v>175843</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="31">
@@ -3538,14 +3688,19 @@
         <v>41408688</v>
       </c>
       <c r="AC31" t="n"/>
-      <c r="AJ31">
-        <f>IF(OR(AB31="",D31="",D31=0),"",AB31/D31)</f>
-        <v/>
+      <c r="AJ31" t="n">
+        <v>0.3661</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Gate=9.5776M | DEX_BSC(PancakeSwap)=31.8311M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=9.5776M | DEX_BSC(PancakeSwap)=31.8311M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$11.655M n=50,987 suspect=0.366x</t>
+        </is>
+      </c>
+      <c r="AP31" t="n">
+        <v>11654883</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>50987</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -3631,14 +3786,19 @@
         <v>8866587</v>
       </c>
       <c r="AC32" t="n"/>
-      <c r="AJ32">
-        <f>IF(OR(AB32="",D32="",D32=0),"",AB32/D32)</f>
-        <v/>
+      <c r="AJ32" t="n">
+        <v>0.0849</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Gate=1.5475M | DEX_BSC(PancakeSwap)=7.3191M | src=GeckoTerminal one-shot 2026-08-03</t>
-        </is>
+          <t>Gate=1.5475M | DEX_BSC(PancakeSwap)=7.3191M | src=GeckoTerminal one-shot 2026-08-03 | alpha_vol=$0.621M n=2,974 suspect=0.085x</t>
+        </is>
+      </c>
+      <c r="AP32" t="n">
+        <v>621160</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>2974</v>
       </c>
     </row>
   </sheetData>

--- a/docs/case_files/CASE_IDOL.xlsx
+++ b/docs/case_files/CASE_IDOL.xlsx
@@ -75,7 +75,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +130,11 @@
         <bgColor rgb="FF375623"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -158,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,6 +215,23 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1038,7 @@
         <v>16584068.48426</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0.4780007889437288</v>
+        <v>47.800079</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>5e-05</v>
@@ -1102,7 +1124,7 @@
         <v>16258105.08826</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.4760134092685071</v>
+        <v>47.601341</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>5e-05</v>
@@ -1191,7 +1213,7 @@
         <v>15289807.35174</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.4987639777670687</v>
+        <v>49.876398</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>0.000333755</v>
@@ -1277,7 +1299,7 @@
         <v>9154051.07804</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.4793609303403439</v>
+        <v>47.936093</v>
       </c>
       <c r="F6" s="19" t="n">
         <v>0.0001978166666666</v>
@@ -1371,7 +1393,7 @@
         <v>8775938.510639999</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.4869234392252542</v>
+        <v>48.692344</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>0.0001027616666666</v>
@@ -1465,7 +1487,7 @@
         <v>3998636.20652</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0.4896940602481673</v>
+        <v>48.969406</v>
       </c>
       <c r="F8" s="19" t="n">
         <v>5e-05</v>
@@ -1562,7 +1584,7 @@
         <v>2234192.34128</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.5182033005451896</v>
+        <v>51.82033</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>0.0001081583333333</v>
@@ -1656,7 +1678,7 @@
         <v>2039666.02208</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>0.5287559261604627</v>
+        <v>52.875593</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>7.325333333333333e-05</v>
@@ -1750,7 +1772,7 @@
         <v>1585348.52764</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.4834225092042596</v>
+        <v>48.342251</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>5e-05</v>
@@ -1848,7 +1870,7 @@
         <v>3092893.51746</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>0.4726014443408847</v>
+        <v>47.260144</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>0.0002229483333333</v>
@@ -1943,7 +1965,7 @@
         <v>5087129.7194</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.4201435632151012</v>
+        <v>42.014356</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>0.00028204</v>
@@ -2038,7 +2060,7 @@
         <v>7737632.26554</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.4939444565350427</v>
+        <v>49.394446</v>
       </c>
       <c r="F14" s="19" t="n">
         <v>0.0001749233333333</v>
@@ -2133,7 +2155,7 @@
         <v>5876711.16144</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.4754047375273049</v>
+        <v>47.540474</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>0.00016166</v>
@@ -2229,7 +2251,7 @@
         <v>2231442.34452</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0.4851628254050874</v>
+        <v>48.516283</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>5e-05</v>
@@ -2327,7 +2349,7 @@
         <v>15102738.57204</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.5092075492693098</v>
+        <v>50.920755</v>
       </c>
       <c r="F17" s="19" t="n">
         <v>0.0001101583333333</v>
@@ -2422,7 +2444,7 @@
         <v>3673663.97688</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0.4874717761027368</v>
+        <v>48.747178</v>
       </c>
       <c r="F18" s="19" t="n">
         <v>0.0001210316666666</v>
@@ -2517,7 +2539,7 @@
         <v>24678006.63704</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.4971711271568416</v>
+        <v>49.717113</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>0.0002538166666666</v>
@@ -2612,7 +2634,7 @@
         <v>8491991.76338</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.4962701448405486</v>
+        <v>49.627014</v>
       </c>
       <c r="F20" s="19" t="n">
         <v>0.0001529483333333</v>
@@ -2706,7 +2728,7 @@
         <v>16647813.36078</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.4870963550740638</v>
+        <v>48.709636</v>
       </c>
       <c r="F21" s="19" t="n">
         <v>0.0001377833333333</v>
@@ -2800,7 +2822,7 @@
         <v>7550669.74948</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>0.4496955742141414</v>
+        <v>44.969557</v>
       </c>
       <c r="F22" s="19" t="n">
         <v>0.0001454166666666</v>
@@ -2894,7 +2916,7 @@
         <v>1919723.54124</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.4756811771186703</v>
+        <v>47.568118</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>5e-05</v>
@@ -2991,7 +3013,7 @@
         <v>1713045.74842</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0.5459623019441526</v>
+        <v>54.59623</v>
       </c>
       <c r="F24" s="19" t="n">
         <v>6.360166666666667e-05</v>
@@ -3085,7 +3107,7 @@
         <v>167259563.39932</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.4890935881891488</v>
+        <v>48.909359</v>
       </c>
       <c r="F25" s="19" t="n">
         <v>0.0002468083333333</v>
@@ -3179,7 +3201,7 @@
         <v>16919045.11194</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>0.4851199670476778</v>
+        <v>48.511997</v>
       </c>
       <c r="F26" s="19" t="n">
         <v>0.0003430716666666</v>
@@ -3273,7 +3295,7 @@
         <v>5930775.03944</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.4801954465121114</v>
+        <v>48.019545</v>
       </c>
       <c r="F27" s="19" t="n">
         <v>0.0001975616666666</v>
@@ -3360,7 +3382,7 @@
         <v>3001087.06951</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.4725181981221648</v>
+        <v>47.25182</v>
       </c>
       <c r="F28" s="19" t="n">
         <v>6.6775e-05</v>
@@ -3447,7 +3469,7 @@
         <v>2995738.46077</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.5284798189362505</v>
+        <v>52.847982</v>
       </c>
       <c r="F29" s="19" t="n">
         <v>9.596166666666668e-05</v>
@@ -3535,7 +3557,7 @@
         <v>7335938.84066</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.4987468671679198</v>
+        <v>49.874687</v>
       </c>
       <c r="F30" s="19" t="n">
         <v>0.00031801</v>
@@ -3625,7 +3647,7 @@
         <v>175671534.50156</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5152925209635985</v>
+        <v>51.529252</v>
       </c>
       <c r="F31" t="n">
         <v>9.492333333333332e-05</v>
@@ -3720,7 +3742,7 @@
         <v>40715280.86713</v>
       </c>
       <c r="E32" t="n">
-        <v>0.500848557452331</v>
+        <v>50.084856</v>
       </c>
       <c r="F32" t="n">
         <v>5e-05</v>
@@ -3800,6 +3822,195 @@
       <c r="AQ32" t="n">
         <v>2974</v>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>0.018868</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>-0.1838021093656651</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>33874473</v>
+      </c>
+      <c r="E33" t="n">
+        <v>44.555</v>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>7.166e-05</v>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H33" s="31" t="n">
+        <v>0.00017046</v>
+      </c>
+      <c r="I33" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>partial_pin</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="33" t="n">
+        <v>9503666</v>
+      </c>
+      <c r="O33" s="29" t="n">
+        <v>1.8049</v>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>1.6539</v>
+      </c>
+      <c r="Q33" s="29" t="n">
+        <v>1.6364</v>
+      </c>
+      <c r="R33" s="34" t="n">
+        <v>1.09129935304432</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n">
+        <v>0.016356</v>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>-0.1331354674581302</v>
+      </c>
+      <c r="D34" s="30" t="n">
+        <v>17027386</v>
+      </c>
+      <c r="E34" t="n">
+        <v>47.177</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>0.0002382</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H34" s="31" t="n">
+        <v>0.00067558</v>
+      </c>
+      <c r="I34" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>spike</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="33" t="n">
+        <v>8825999</v>
+      </c>
+      <c r="O34" s="29" t="n">
+        <v>1.7453</v>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>1.6274</v>
+      </c>
+      <c r="Q34" s="29" t="n">
+        <v>1.4612</v>
+      </c>
+      <c r="R34" s="34" t="n">
+        <v>1.07244684773258</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="C35" s="37" t="n">
+        <v>-0.01687454145267786</v>
+      </c>
+      <c r="D35" s="38" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E35" s="39" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="40" t="n"/>
+      <c r="I35" s="41" t="n"/>
+      <c r="J35" s="39" t="inlineStr">
+        <is>
+          <t>near_zero</t>
+        </is>
+      </c>
+      <c r="K35" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="42" t="n">
+        <v>8866000</v>
+      </c>
+      <c r="M35" s="39" t="n"/>
+      <c r="N35" s="39" t="n"/>
+      <c r="O35" s="37" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="P35" s="37" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="Q35" s="37" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="R35" s="43" t="n">
+        <v>1.392586989409985</v>
+      </c>
+      <c r="S35" s="39" t="n"/>
+      <c r="T35" s="39" t="n"/>
+      <c r="U35" s="39" t="n"/>
+      <c r="V35" s="39" t="n"/>
+      <c r="W35" s="39" t="n"/>
+      <c r="X35" s="39" t="n"/>
+      <c r="Y35" s="39" t="n"/>
+      <c r="Z35" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="39" t="n"/>
+      <c r="AB35" s="39" t="n"/>
+      <c r="AC35" s="39" t="n"/>
+      <c r="AD35" s="39" t="n"/>
+      <c r="AE35" s="39" t="n"/>
+      <c r="AF35" s="39" t="n"/>
+      <c r="AG35" s="39" t="n"/>
+      <c r="AH35" s="39" t="n"/>
+      <c r="AI35" s="39" t="n"/>
+      <c r="AJ35" s="39" t="n"/>
+      <c r="AK35" s="39" t="n"/>
+      <c r="AL35" s="39" t="n"/>
+      <c r="AM35" s="39" t="n"/>
+      <c r="AN35" s="39" t="n"/>
+      <c r="AO35" s="39" t="n"/>
+      <c r="AP35" s="39" t="n"/>
+      <c r="AQ35" s="39" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3814,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3933,6 +4144,72 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Suppressor context thường trực: 2%/tháng ngày 11. Markup 01/08 nổ 10 ngày TRƯỚC — unlock ≠ trigger E1 (W6: UNLIKELY). Nguồn: CoinLaunch (op-verified). Team/Strat/Priv vừa ra linear post-cliff 06/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>58bro: nhan 27.06M tokens -&gt; NAP LAI 27.06M cung ngay (roundtrip net=0). Cung ngay nhan them 10M + 14.3M = 24.3M (giu lai, chua nap)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>operator_screenshot_20260806</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[THONG DIEP?] Gate-&gt;vi-&gt;Gate roundtrip 27.06M = ao cu Loai A; net giu: 24.3M — pending verify co nap tiep khong</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>58bro: nhan 8.14M tokens (giu lai, chua nap theo screenshot)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>operator_screenshot_20260806</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tong net moi giu (04-06/08): 10M+14.3M+8.14M=32.44M — pending balance check sau 06/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Y4 PENDING: dia chi vi smart-money operator thay dang gom — can doi chieu cum 13 vi staging + 58bro + Gate 0x0d0707</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Loai A confirmed: moi on-chain tu he vi cu = THONG DIEP; chi vi ngoai he + swap DEX thuc moi dem</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_IDOL.xlsx
+++ b/docs/case_files/CASE_IDOL.xlsx
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AQ42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4012,6 +4012,482 @@
       <c r="AP35" s="39" t="n"/>
       <c r="AQ35" s="39" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0165597765259032</v>
+      </c>
+      <c r="C36">
+        <f>IFERROR(B36/B35-1,"")</f>
+        <v/>
+      </c>
+      <c r="D36" t="n">
+        <v>1422405.15105</v>
+      </c>
+      <c r="E36" t="n">
+        <v>51.996928</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0002341283333333</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0001196</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00040116</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8923116.358337641</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.9121</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.7685</v>
+      </c>
+      <c r="R36">
+        <f>IFERROR(O36/P36,"")</f>
+        <v/>
+      </c>
+      <c r="S36">
+        <f>IFERROR(AVERAGE(R34:R36),"")</f>
+        <v/>
+      </c>
+      <c r="T36">
+        <f>IFERROR(Q36/Q31,"")</f>
+        <v/>
+      </c>
+      <c r="U36">
+        <f>IFERROR(O36/O33-1,"")</f>
+        <v/>
+      </c>
+      <c r="V36">
+        <f>IFERROR(P36/P33-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ36">
+        <f>IF(OR(AB36="",D36="",D36=0),"",AB36/D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0167483576192693</v>
+      </c>
+      <c r="C37">
+        <f>IFERROR(B37/B36-1,"")</f>
+        <v/>
+      </c>
+      <c r="D37" t="n">
+        <v>2155991.79121</v>
+      </c>
+      <c r="E37" t="n">
+        <v>49.148233</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0002020633333333</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00047835</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9228931.327299999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.9641</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.5549</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.5082</v>
+      </c>
+      <c r="R37">
+        <f>IFERROR(O37/P37,"")</f>
+        <v/>
+      </c>
+      <c r="S37">
+        <f>IFERROR(AVERAGE(R35:R37),"")</f>
+        <v/>
+      </c>
+      <c r="T37">
+        <f>IFERROR(Q37/Q32,"")</f>
+        <v/>
+      </c>
+      <c r="U37">
+        <f>IFERROR(O37/O34-1,"")</f>
+        <v/>
+      </c>
+      <c r="V37">
+        <f>IFERROR(P37/P34-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ37">
+        <f>IF(OR(AB37="",D37="",D37=0),"",AB37/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0166013754868437</v>
+      </c>
+      <c r="C38">
+        <f>IFERROR(B38/B37-1,"")</f>
+        <v/>
+      </c>
+      <c r="D38" t="n">
+        <v>2067061.31726</v>
+      </c>
+      <c r="E38" t="n">
+        <v>46.300075</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0001120533333333</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00021229</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9062055.865902221</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.9798</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.5628</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.5284</v>
+      </c>
+      <c r="R38">
+        <f>IFERROR(O38/P38,"")</f>
+        <v/>
+      </c>
+      <c r="S38">
+        <f>IFERROR(AVERAGE(R36:R38),"")</f>
+        <v/>
+      </c>
+      <c r="T38">
+        <f>IFERROR(Q38/Q33,"")</f>
+        <v/>
+      </c>
+      <c r="U38">
+        <f>IFERROR(O38/O35-1,"")</f>
+        <v/>
+      </c>
+      <c r="V38">
+        <f>IFERROR(P38/P35-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ38">
+        <f>IF(OR(AB38="",D38="",D38=0),"",AB38/D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0164812247888463</v>
+      </c>
+      <c r="C39">
+        <f>IFERROR(B39/B38-1,"")</f>
+        <v/>
+      </c>
+      <c r="D39" t="n">
+        <v>1167674.19124</v>
+      </c>
+      <c r="E39" t="n">
+        <v>51.971567</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.00014245</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00031837</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8846186.45356</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.7345</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.6724</v>
+      </c>
+      <c r="R39">
+        <f>IFERROR(O39/P39,"")</f>
+        <v/>
+      </c>
+      <c r="S39">
+        <f>IFERROR(AVERAGE(R37:R39),"")</f>
+        <v/>
+      </c>
+      <c r="T39">
+        <f>IFERROR(Q39/Q34,"")</f>
+        <v/>
+      </c>
+      <c r="U39">
+        <f>IFERROR(O39/O36-1,"")</f>
+        <v/>
+      </c>
+      <c r="V39">
+        <f>IFERROR(P39/P36-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ39">
+        <f>IF(OR(AB39="",D39="",D39=0),"",AB39/D39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0173237557259619</v>
+      </c>
+      <c r="C40">
+        <f>IFERROR(B40/B39-1,"")</f>
+        <v/>
+      </c>
+      <c r="D40" t="n">
+        <v>2515289.31243</v>
+      </c>
+      <c r="E40" t="n">
+        <v>51.097853</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0002004716666666</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00035637</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8875114.029929999</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.9889</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.8736</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.8249</v>
+      </c>
+      <c r="R40">
+        <f>IFERROR(O40/P40,"")</f>
+        <v/>
+      </c>
+      <c r="S40">
+        <f>IFERROR(AVERAGE(R38:R40),"")</f>
+        <v/>
+      </c>
+      <c r="T40">
+        <f>IFERROR(Q40/Q35,"")</f>
+        <v/>
+      </c>
+      <c r="U40">
+        <f>IFERROR(O40/O37-1,"")</f>
+        <v/>
+      </c>
+      <c r="V40">
+        <f>IFERROR(P40/P37-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ40">
+        <f>IF(OR(AB40="",D40="",D40=0),"",AB40/D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0169496893471147</v>
+      </c>
+      <c r="C41">
+        <f>IFERROR(B41/B40-1,"")</f>
+        <v/>
+      </c>
+      <c r="D41" t="n">
+        <v>1592367.19374</v>
+      </c>
+      <c r="E41" t="n">
+        <v>49.230847</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0002438416666666</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.00051894</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8828942.783625839</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.9694</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.2744</v>
+      </c>
+      <c r="R41">
+        <f>IFERROR(O41/P41,"")</f>
+        <v/>
+      </c>
+      <c r="S41">
+        <f>IFERROR(AVERAGE(R39:R41),"")</f>
+        <v/>
+      </c>
+      <c r="T41">
+        <f>IFERROR(Q41/Q36,"")</f>
+        <v/>
+      </c>
+      <c r="U41">
+        <f>IFERROR(O41/O38-1,"")</f>
+        <v/>
+      </c>
+      <c r="V41">
+        <f>IFERROR(P41/P38-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ41">
+        <f>IF(OR(AB41="",D41="",D41=0),"",AB41/D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.01718659678838011</v>
+      </c>
+      <c r="C42">
+        <f>IFERROR(B42/B41-1,"")</f>
+        <v/>
+      </c>
+      <c r="D42" t="n">
+        <v>757012.5634</v>
+      </c>
+      <c r="E42" t="n">
+        <v>49.655138</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0003208266666666667</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.00010502</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.00051527</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8812072.0475742</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.8469</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.1104</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.2082</v>
+      </c>
+      <c r="R42">
+        <f>IFERROR(O42/P42,"")</f>
+        <v/>
+      </c>
+      <c r="S42">
+        <f>IFERROR(AVERAGE(R40:R42),"")</f>
+        <v/>
+      </c>
+      <c r="T42">
+        <f>IFERROR(Q42/Q37,"")</f>
+        <v/>
+      </c>
+      <c r="U42">
+        <f>IFERROR(O42/O39-1,"")</f>
+        <v/>
+      </c>
+      <c r="V42">
+        <f>IFERROR(P42/P39-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ42">
+        <f>IF(OR(AB42="",D42="",D42=0),"",AB42/D42)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
